--- a/Fig.3(e).xlsx
+++ b/Fig.3(e).xlsx
@@ -537,7 +537,7 @@
         <v>60.9375</v>
       </c>
       <c r="R6">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="S6">
         <v>60.9375</v>
@@ -3609,7 +3609,7 @@
         <v>42.1875</v>
       </c>
       <c r="AX18">
-        <v>1.2999999999999999E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="AY18">
         <v>42.1875</v>
@@ -4565,7 +4565,7 @@
         <v>35.9375</v>
       </c>
       <c r="AL22" s="1">
-        <v>7.1472599999999999E-6</v>
+        <v>7.1472799999999996E-6</v>
       </c>
       <c r="AM22">
         <v>35.9375</v>
@@ -4813,7 +4813,7 @@
         <v>34.375</v>
       </c>
       <c r="AL23" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5736399999999998E-6</v>
       </c>
       <c r="AM23">
         <v>34.375</v>
@@ -4849,7 +4849,7 @@
         <v>34.375</v>
       </c>
       <c r="AX23" s="1">
-        <v>2.5015400000000001E-5</v>
+        <v>2.5015600000000002E-5</v>
       </c>
       <c r="AY23" s="1">
         <v>34.375</v>
@@ -5061,7 +5061,7 @@
         <v>32.8125</v>
       </c>
       <c r="AL24" s="1">
-        <v>-3.57363E-6</v>
+        <v>-3.5736399999999998E-6</v>
       </c>
       <c r="AM24">
         <v>32.8125</v>
@@ -5097,13 +5097,13 @@
         <v>32.8125</v>
       </c>
       <c r="AX24" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5736700000000002E-6</v>
       </c>
       <c r="AY24" s="1">
         <v>32.8125</v>
       </c>
       <c r="AZ24" s="1">
-        <v>3.57363E-6</v>
+        <v>3.4155600000000001E-6</v>
       </c>
       <c r="BA24">
         <v>32.8125</v>
@@ -5309,7 +5309,7 @@
         <v>31.25</v>
       </c>
       <c r="AL25" s="1">
-        <v>-3.57363E-6</v>
+        <v>-3.5736399999999998E-6</v>
       </c>
       <c r="AM25">
         <v>31.25</v>
@@ -5599,7 +5599,7 @@
         <v>29.6875</v>
       </c>
       <c r="AZ26" s="1">
-        <v>0</v>
+        <v>4.8200299999999998E-7</v>
       </c>
       <c r="BA26">
         <v>29.6875</v>
@@ -5745,7 +5745,7 @@
         <v>28.125</v>
       </c>
       <c r="R27">
-        <v>1.32E-3</v>
+        <v>2.2300000000000002E-3</v>
       </c>
       <c r="S27">
         <v>28.125</v>
@@ -5993,7 +5993,7 @@
         <v>26.5625</v>
       </c>
       <c r="R28" s="1">
-        <v>7.26E-3</v>
+        <v>1.166E-2</v>
       </c>
       <c r="S28" s="1">
         <v>26.5625</v>
@@ -6053,7 +6053,7 @@
         <v>26.5625</v>
       </c>
       <c r="AL28" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5736399999999998E-6</v>
       </c>
       <c r="AM28">
         <v>26.5625</v>
@@ -6089,13 +6089,13 @@
         <v>26.5625</v>
       </c>
       <c r="AX28" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5736700000000002E-6</v>
       </c>
       <c r="AY28">
         <v>26.5625</v>
       </c>
       <c r="AZ28" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5735600000000001E-6</v>
       </c>
       <c r="BA28">
         <v>26.5625</v>
@@ -6113,7 +6113,7 @@
         <v>26.5625</v>
       </c>
       <c r="BF28" s="1">
-        <v>0</v>
+        <v>1.62003E-7</v>
       </c>
       <c r="BG28" s="1">
         <v>26.5625</v>
@@ -6241,7 +6241,7 @@
         <v>25</v>
       </c>
       <c r="R29" s="1">
-        <v>1.115E-2</v>
+        <v>1.0240000000000001E-2</v>
       </c>
       <c r="S29" s="1">
         <v>25</v>
@@ -6301,7 +6301,7 @@
         <v>25</v>
       </c>
       <c r="AL29" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5736399999999998E-6</v>
       </c>
       <c r="AM29">
         <v>25</v>
@@ -6337,13 +6337,13 @@
         <v>25</v>
       </c>
       <c r="AX29" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5736700000000002E-6</v>
       </c>
       <c r="AY29">
         <v>25</v>
       </c>
       <c r="AZ29" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5735600000000001E-6</v>
       </c>
       <c r="BA29">
         <v>25</v>
@@ -6489,7 +6489,7 @@
         <v>23.4375</v>
       </c>
       <c r="R30" s="1">
-        <v>4.5799999999999999E-3</v>
+        <v>1.79075E-4</v>
       </c>
       <c r="S30" s="1">
         <v>23.4375</v>
@@ -6797,7 +6797,7 @@
         <v>21.875</v>
       </c>
       <c r="AL31" s="1">
-        <v>-3.57363E-6</v>
+        <v>-3.5736399999999998E-6</v>
       </c>
       <c r="AM31">
         <v>21.875</v>
@@ -7045,7 +7045,7 @@
         <v>20.3125</v>
       </c>
       <c r="AL32" s="1">
-        <v>-3.57363E-6</v>
+        <v>-3.5736399999999998E-6</v>
       </c>
       <c r="AM32">
         <v>20.3125</v>
@@ -7105,7 +7105,7 @@
         <v>20.3125</v>
       </c>
       <c r="BF32" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5735600000000001E-6</v>
       </c>
       <c r="BG32" s="1">
         <v>20.3125</v>
@@ -7541,7 +7541,7 @@
         <v>17.1875</v>
       </c>
       <c r="AL34" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5736399999999998E-6</v>
       </c>
       <c r="AM34">
         <v>17.1875</v>
@@ -7789,7 +7789,7 @@
         <v>15.625</v>
       </c>
       <c r="AL35" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5736399999999998E-6</v>
       </c>
       <c r="AM35">
         <v>15.625</v>
@@ -7849,7 +7849,7 @@
         <v>15.625</v>
       </c>
       <c r="BF35" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5735600000000001E-6</v>
       </c>
       <c r="BG35">
         <v>15.625</v>
@@ -8285,7 +8285,7 @@
         <v>12.5</v>
       </c>
       <c r="AL37" s="1">
-        <v>-3.57363E-6</v>
+        <v>-3.5736399999999998E-6</v>
       </c>
       <c r="AM37">
         <v>12.5</v>
@@ -8533,7 +8533,7 @@
         <v>10.9375</v>
       </c>
       <c r="AL38" s="1">
-        <v>-3.57363E-6</v>
+        <v>-3.5736399999999998E-6</v>
       </c>
       <c r="AM38">
         <v>10.9375</v>
@@ -9277,7 +9277,7 @@
         <v>6.25</v>
       </c>
       <c r="AL41" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5736399999999998E-6</v>
       </c>
       <c r="AM41">
         <v>6.25</v>
@@ -9525,7 +9525,7 @@
         <v>4.6875</v>
       </c>
       <c r="AL42" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5736399999999998E-6</v>
       </c>
       <c r="AM42">
         <v>4.6875</v>
@@ -9773,7 +9773,7 @@
         <v>3.125</v>
       </c>
       <c r="AL43" s="1">
-        <v>-3.57363E-6</v>
+        <v>-3.5736399999999998E-6</v>
       </c>
       <c r="AM43">
         <v>3.125</v>
@@ -9919,7 +9919,7 @@
         <v>1.5625</v>
       </c>
       <c r="D44" s="1">
-        <v>4.3857100000000001E-4</v>
+        <v>4.3860200000000001E-4</v>
       </c>
       <c r="E44">
         <v>1.5625</v>
@@ -10063,7 +10063,7 @@
         <v>1.5625</v>
       </c>
       <c r="AZ44" s="1">
-        <v>0</v>
+        <v>-3.5735600000000001E-6</v>
       </c>
       <c r="BA44">
         <v>1.5625</v>
@@ -10167,7 +10167,7 @@
         <v>0</v>
       </c>
       <c r="D45" s="1">
-        <v>5.4727499999999995E-4</v>
+        <v>5.4731400000000003E-4</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -10269,7 +10269,7 @@
         <v>0</v>
       </c>
       <c r="AL45" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5736399999999998E-6</v>
       </c>
       <c r="AM45">
         <v>0</v>
@@ -10305,13 +10305,13 @@
         <v>0</v>
       </c>
       <c r="AX45" s="1">
-        <v>0</v>
+        <v>-3.5736700000000002E-6</v>
       </c>
       <c r="AY45" s="1">
         <v>0</v>
       </c>
       <c r="AZ45" s="1">
-        <v>0</v>
+        <v>-3.5735600000000001E-6</v>
       </c>
       <c r="BA45">
         <v>0</v>
@@ -10329,7 +10329,7 @@
         <v>0</v>
       </c>
       <c r="BF45" s="1">
-        <v>-3.57363E-6</v>
+        <v>-3.5735600000000001E-6</v>
       </c>
       <c r="BG45" s="1">
         <v>0</v>
@@ -10553,7 +10553,7 @@
         <v>-1.5625</v>
       </c>
       <c r="AX46" s="1">
-        <v>0</v>
+        <v>-3.5736700000000002E-6</v>
       </c>
       <c r="AY46" s="1">
         <v>-1.5625</v>
@@ -10577,7 +10577,7 @@
         <v>-1.5625</v>
       </c>
       <c r="BF46" s="1">
-        <v>-3.57363E-6</v>
+        <v>-3.5735600000000001E-6</v>
       </c>
       <c r="BG46" s="1">
         <v>-1.5625</v>
@@ -11055,7 +11055,7 @@
         <v>-4.6875</v>
       </c>
       <c r="AZ48" s="1">
-        <v>0</v>
+        <v>-6.4000000000000002E-9</v>
       </c>
       <c r="BA48">
         <v>-4.6875</v>
@@ -11073,7 +11073,7 @@
         <v>-4.6875</v>
       </c>
       <c r="BF48" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5735600000000001E-6</v>
       </c>
       <c r="BG48">
         <v>-4.6875</v>
@@ -11321,7 +11321,7 @@
         <v>-6.25</v>
       </c>
       <c r="BF49" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5735600000000001E-6</v>
       </c>
       <c r="BG49">
         <v>-6.25</v>
@@ -11551,7 +11551,7 @@
         <v>-7.8125</v>
       </c>
       <c r="AZ50" s="1">
-        <v>0</v>
+        <v>6.4000000000000002E-9</v>
       </c>
       <c r="BA50">
         <v>-7.8125</v>
@@ -12041,13 +12041,13 @@
         <v>-10.9375</v>
       </c>
       <c r="AX52" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5736700000000002E-6</v>
       </c>
       <c r="AY52">
         <v>-10.9375</v>
       </c>
       <c r="AZ52" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5735600000000001E-6</v>
       </c>
       <c r="BA52">
         <v>-10.9375</v>
@@ -12289,13 +12289,13 @@
         <v>-12.5</v>
       </c>
       <c r="AX53" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5736700000000002E-6</v>
       </c>
       <c r="AY53">
         <v>-12.5</v>
       </c>
       <c r="AZ53" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5735600000000001E-6</v>
       </c>
       <c r="BA53">
         <v>-12.5</v>
@@ -12689,7 +12689,7 @@
         <v>-15.625</v>
       </c>
       <c r="R55" s="1">
-        <v>2.85889E-5</v>
+        <v>2.8589E-5</v>
       </c>
       <c r="S55">
         <v>-15.625</v>
@@ -12937,7 +12937,7 @@
         <v>-17.1875</v>
       </c>
       <c r="R56" s="1">
-        <v>7.5046100000000006E-5</v>
+        <v>3.2599999999999999E-3</v>
       </c>
       <c r="S56">
         <v>-17.1875</v>
@@ -13185,7 +13185,7 @@
         <v>-18.75</v>
       </c>
       <c r="R57">
-        <v>5.2300000000000003E-3</v>
+        <v>7.8100000000000001E-3</v>
       </c>
       <c r="S57">
         <v>-18.75</v>
@@ -13433,7 +13433,7 @@
         <v>-20.3125</v>
       </c>
       <c r="R58">
-        <v>9.1299999999999992E-3</v>
+        <v>5.94E-3</v>
       </c>
       <c r="S58">
         <v>-20.3125</v>
@@ -13681,7 +13681,7 @@
         <v>-21.875</v>
       </c>
       <c r="R59">
-        <v>4.6100000000000004E-3</v>
+        <v>2.0300000000000001E-3</v>
       </c>
       <c r="S59">
         <v>-21.875</v>
@@ -14769,13 +14769,13 @@
         <v>-28.125</v>
       </c>
       <c r="AX63" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5736700000000002E-6</v>
       </c>
       <c r="AY63">
         <v>-28.125</v>
       </c>
       <c r="AZ63" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5735600000000001E-6</v>
       </c>
       <c r="BA63">
         <v>-28.125</v>
@@ -15017,7 +15017,7 @@
         <v>-29.6875</v>
       </c>
       <c r="AX64" s="1">
-        <v>1.42945E-5</v>
+        <v>1.42946E-5</v>
       </c>
       <c r="AY64">
         <v>-29.6875</v>
@@ -15271,7 +15271,7 @@
         <v>-31.25</v>
       </c>
       <c r="AZ65">
-        <v>1.375E-2</v>
+        <v>1.374E-2</v>
       </c>
       <c r="BA65">
         <v>-31.25</v>
@@ -15477,7 +15477,7 @@
         <v>-32.8125</v>
       </c>
       <c r="AL66" s="1">
-        <v>7.1472599999999999E-6</v>
+        <v>7.1472799999999996E-6</v>
       </c>
       <c r="AM66">
         <v>-32.8125</v>
@@ -15513,7 +15513,7 @@
         <v>-32.8125</v>
       </c>
       <c r="AX66">
-        <v>1.439E-2</v>
+        <v>1.44E-2</v>
       </c>
       <c r="AY66">
         <v>-32.8125</v>

--- a/Fig.3(e).xlsx
+++ b/Fig.3(e).xlsx
@@ -24,12 +24,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
   <si>
     <t>I</t>
   </si>
   <si>
     <t>dV/dI</t>
+  </si>
+  <si>
+    <t>--</t>
   </si>
 </sst>
 </file>
@@ -348,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CD84"/>
+  <dimension ref="A1:CD85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:82" x14ac:dyDescent="0.25">
@@ -1051,7 +1054,7 @@
         <v>57.8125</v>
       </c>
       <c r="X8">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="Y8">
         <v>57.8125</v>
@@ -1795,7 +1798,7 @@
         <v>53.125</v>
       </c>
       <c r="X11">
-        <v>1.2999999999999999E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="Y11">
         <v>53.125</v>
@@ -2787,7 +2790,7 @@
         <v>46.875</v>
       </c>
       <c r="X15">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="Y15">
         <v>46.875</v>
@@ -3283,7 +3286,7 @@
         <v>43.75</v>
       </c>
       <c r="X17">
-        <v>1.31E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="Y17">
         <v>43.75</v>
@@ -4027,7 +4030,7 @@
         <v>39.0625</v>
       </c>
       <c r="X20">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="Y20">
         <v>39.0625</v>
@@ -4275,7 +4278,7 @@
         <v>37.5</v>
       </c>
       <c r="X21">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="Y21">
         <v>37.5</v>
@@ -4523,7 +4526,7 @@
         <v>35.9375</v>
       </c>
       <c r="X22">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="Y22">
         <v>35.9375</v>
@@ -4767,10 +4770,10 @@
       <c r="V23">
         <v>1.32E-3</v>
       </c>
-      <c r="W23">
+      <c r="W23" s="1">
         <v>34.375</v>
       </c>
-      <c r="X23">
+      <c r="X23" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="Y23">
@@ -5015,11 +5018,11 @@
       <c r="V24">
         <v>1.31E-3</v>
       </c>
-      <c r="W24">
+      <c r="W24" s="1">
         <v>32.8125</v>
       </c>
-      <c r="X24">
-        <v>1.2999999999999999E-3</v>
+      <c r="X24" s="1">
+        <v>1.31E-3</v>
       </c>
       <c r="Y24">
         <v>32.8125</v>
@@ -5267,7 +5270,7 @@
         <v>31.25</v>
       </c>
       <c r="X25" s="1">
-        <v>1.5399999999999999E-3</v>
+        <v>3.5599999999999998E-3</v>
       </c>
       <c r="Y25" s="1">
         <v>31.25</v>
@@ -5511,11 +5514,11 @@
       <c r="V26" s="1">
         <v>1.3129999999999999E-2</v>
       </c>
-      <c r="W26" s="1">
+      <c r="W26">
         <v>29.6875</v>
       </c>
-      <c r="X26" s="1">
-        <v>1.7600000000000001E-3</v>
+      <c r="X26">
+        <v>1.3089999999999999E-2</v>
       </c>
       <c r="Y26" s="1">
         <v>29.6875</v>
@@ -5759,11 +5762,11 @@
       <c r="V27" s="1">
         <v>8.7799999999999996E-3</v>
       </c>
-      <c r="W27" s="1">
+      <c r="W27">
         <v>28.125</v>
       </c>
-      <c r="X27" s="1">
-        <v>2.15E-3</v>
+      <c r="X27">
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="Y27" s="1">
         <v>28.125</v>
@@ -6010,8 +6013,8 @@
       <c r="W28">
         <v>26.5625</v>
       </c>
-      <c r="X28">
-        <v>1.136E-2</v>
+      <c r="X28" s="1">
+        <v>2.6155800000000001E-5</v>
       </c>
       <c r="Y28">
         <v>26.5625</v>
@@ -6258,8 +6261,8 @@
       <c r="W29">
         <v>25</v>
       </c>
-      <c r="X29">
-        <v>1.009E-2</v>
+      <c r="X29" s="1">
+        <v>1.12097E-5</v>
       </c>
       <c r="Y29">
         <v>25</v>
@@ -6506,8 +6509,8 @@
       <c r="W30">
         <v>23.4375</v>
       </c>
-      <c r="X30">
-        <v>0</v>
+      <c r="X30" s="1">
+        <v>3.7365799999999998E-6</v>
       </c>
       <c r="Y30">
         <v>23.4375</v>
@@ -8983,10 +8986,10 @@
       <c r="V40">
         <v>0</v>
       </c>
-      <c r="W40">
+      <c r="W40" s="1">
         <v>7.8125</v>
       </c>
-      <c r="X40">
+      <c r="X40" s="1">
         <v>0</v>
       </c>
       <c r="Y40">
@@ -9231,10 +9234,10 @@
       <c r="V41">
         <v>0</v>
       </c>
-      <c r="W41">
+      <c r="W41" s="1">
         <v>6.25</v>
       </c>
-      <c r="X41">
+      <c r="X41" s="1">
         <v>0</v>
       </c>
       <c r="Y41">
@@ -9479,10 +9482,10 @@
       <c r="V42">
         <v>0</v>
       </c>
-      <c r="W42" s="1">
+      <c r="W42">
         <v>4.6875</v>
       </c>
-      <c r="X42" s="1">
+      <c r="X42">
         <v>0</v>
       </c>
       <c r="Y42">
@@ -9727,10 +9730,10 @@
       <c r="V43" s="1">
         <v>0</v>
       </c>
-      <c r="W43" s="1">
+      <c r="W43">
         <v>3.125</v>
       </c>
-      <c r="X43" s="1">
+      <c r="X43">
         <v>0</v>
       </c>
       <c r="Y43" s="1">
@@ -10226,8 +10229,8 @@
       <c r="W45">
         <v>0</v>
       </c>
-      <c r="X45">
-        <v>0</v>
+      <c r="X45" t="s">
+        <v>2</v>
       </c>
       <c r="Y45">
         <v>0</v>
@@ -10472,10 +10475,10 @@
         <v>3.57363E-6</v>
       </c>
       <c r="W46">
-        <v>-1.5625</v>
-      </c>
-      <c r="X46">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="X46" t="s">
+        <v>2</v>
       </c>
       <c r="Y46">
         <v>-1.5625</v>
@@ -10720,7 +10723,7 @@
         <v>3.57363E-6</v>
       </c>
       <c r="W47">
-        <v>-3.125</v>
+        <v>-1.5625</v>
       </c>
       <c r="X47">
         <v>0</v>
@@ -10968,7 +10971,7 @@
         <v>0</v>
       </c>
       <c r="W48">
-        <v>-4.6875</v>
+        <v>-3.125</v>
       </c>
       <c r="X48">
         <v>0</v>
@@ -11216,9 +11219,9 @@
         <v>0</v>
       </c>
       <c r="W49">
-        <v>-6.25</v>
-      </c>
-      <c r="X49">
+        <v>-4.6875</v>
+      </c>
+      <c r="X49" s="1">
         <v>0</v>
       </c>
       <c r="Y49">
@@ -11463,10 +11466,10 @@
       <c r="V50">
         <v>0</v>
       </c>
-      <c r="W50">
-        <v>-7.8125</v>
-      </c>
-      <c r="X50">
+      <c r="W50" s="1">
+        <v>-6.25</v>
+      </c>
+      <c r="X50" s="1">
         <v>0</v>
       </c>
       <c r="Y50">
@@ -11711,8 +11714,8 @@
       <c r="V51">
         <v>0</v>
       </c>
-      <c r="W51">
-        <v>-9.375</v>
+      <c r="W51" s="1">
+        <v>-7.8125</v>
       </c>
       <c r="X51" s="1">
         <v>0</v>
@@ -11960,7 +11963,7 @@
         <v>0</v>
       </c>
       <c r="W52" s="1">
-        <v>-10.9375</v>
+        <v>-9.375</v>
       </c>
       <c r="X52" s="1">
         <v>0</v>
@@ -12208,7 +12211,7 @@
         <v>0</v>
       </c>
       <c r="W53" s="1">
-        <v>-12.5</v>
+        <v>-10.9375</v>
       </c>
       <c r="X53" s="1">
         <v>0</v>
@@ -12455,11 +12458,11 @@
       <c r="V54" s="1">
         <v>0</v>
       </c>
-      <c r="W54" s="1">
-        <v>-14.0625</v>
+      <c r="W54">
+        <v>-12.5</v>
       </c>
       <c r="X54" s="1">
-        <v>3.7366200000000001E-6</v>
+        <v>0</v>
       </c>
       <c r="Y54" s="1">
         <v>-14.0625</v>
@@ -12703,11 +12706,11 @@
       <c r="V55" s="1">
         <v>0</v>
       </c>
-      <c r="W55" s="1">
-        <v>-15.625</v>
+      <c r="W55">
+        <v>-14.0625</v>
       </c>
       <c r="X55" s="1">
-        <v>3.7042999999999998E-6</v>
+        <v>3.7365799999999998E-6</v>
       </c>
       <c r="Y55" s="1">
         <v>-15.625</v>
@@ -12952,10 +12955,10 @@
         <v>3.57363E-6</v>
       </c>
       <c r="W56">
-        <v>-17.1875</v>
+        <v>-15.625</v>
       </c>
       <c r="X56" s="1">
-        <v>3.7484599999999999E-6</v>
+        <v>3.7365799999999998E-6</v>
       </c>
       <c r="Y56" s="1">
         <v>-17.1875</v>
@@ -13200,10 +13203,10 @@
         <v>7.1472599999999999E-6</v>
       </c>
       <c r="W57">
-        <v>-18.75</v>
+        <v>-17.1875</v>
       </c>
       <c r="X57" s="1">
-        <v>1.98401E-5</v>
+        <v>3.7365799999999998E-6</v>
       </c>
       <c r="Y57">
         <v>-18.75</v>
@@ -13448,10 +13451,10 @@
         <v>1.0720899999999999E-5</v>
       </c>
       <c r="W58">
-        <v>-20.3125</v>
-      </c>
-      <c r="X58">
-        <v>9.1699999999999993E-3</v>
+        <v>-18.75</v>
+      </c>
+      <c r="X58" s="1">
+        <v>1.12094E-5</v>
       </c>
       <c r="Y58">
         <v>-20.3125</v>
@@ -13696,10 +13699,10 @@
         <v>3.9309800000000001E-5</v>
       </c>
       <c r="W59">
-        <v>-21.875</v>
-      </c>
-      <c r="X59">
-        <v>9.6200000000000001E-3</v>
+        <v>-20.3125</v>
+      </c>
+      <c r="X59" s="1">
+        <v>4.0786199999999999E-5</v>
       </c>
       <c r="Y59">
         <v>-21.875</v>
@@ -13944,10 +13947,10 @@
         <v>6.6499999999999997E-3</v>
       </c>
       <c r="W60">
-        <v>-23.4375</v>
-      </c>
-      <c r="X60">
-        <v>1.16E-3</v>
+        <v>-21.875</v>
+      </c>
+      <c r="X60" s="1">
+        <v>3.1650499999999999E-6</v>
       </c>
       <c r="Y60">
         <v>-23.4375</v>
@@ -14192,10 +14195,10 @@
         <v>1.1129999999999999E-2</v>
       </c>
       <c r="W61">
-        <v>-25</v>
-      </c>
-      <c r="X61">
-        <v>1.5E-3</v>
+        <v>-23.4375</v>
+      </c>
+      <c r="X61" s="1">
+        <v>1.8718399999999999E-4</v>
       </c>
       <c r="Y61">
         <v>-25</v>
@@ -14440,10 +14443,10 @@
         <v>5.1700000000000001E-3</v>
       </c>
       <c r="W62">
-        <v>-26.5625</v>
+        <v>-25</v>
       </c>
       <c r="X62">
-        <v>1.4599999999999999E-3</v>
+        <v>1.1129999999999999E-2</v>
       </c>
       <c r="Y62">
         <v>-26.5625</v>
@@ -14688,10 +14691,10 @@
         <v>1.32E-3</v>
       </c>
       <c r="W63">
-        <v>-28.125</v>
+        <v>-26.5625</v>
       </c>
       <c r="X63">
-        <v>1.31E-3</v>
+        <v>1.157E-2</v>
       </c>
       <c r="Y63">
         <v>-28.125</v>
@@ -14936,7 +14939,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="W64">
-        <v>-29.6875</v>
+        <v>-28.125</v>
       </c>
       <c r="X64">
         <v>1.31E-3</v>
@@ -15184,7 +15187,7 @@
         <v>1.31E-3</v>
       </c>
       <c r="W65">
-        <v>-31.25</v>
+        <v>-29.6875</v>
       </c>
       <c r="X65">
         <v>1.31E-3</v>
@@ -15432,7 +15435,7 @@
         <v>1.31E-3</v>
       </c>
       <c r="W66">
-        <v>-32.8125</v>
+        <v>-31.25</v>
       </c>
       <c r="X66">
         <v>1.31E-3</v>
@@ -15680,7 +15683,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="W67">
-        <v>-34.375</v>
+        <v>-32.8125</v>
       </c>
       <c r="X67">
         <v>1.31E-3</v>
@@ -15928,7 +15931,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="W68">
-        <v>-35.9375</v>
+        <v>-34.375</v>
       </c>
       <c r="X68">
         <v>1.31E-3</v>
@@ -16176,7 +16179,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="W69">
-        <v>-37.5</v>
+        <v>-35.9375</v>
       </c>
       <c r="X69">
         <v>1.31E-3</v>
@@ -16424,10 +16427,10 @@
         <v>1.32E-3</v>
       </c>
       <c r="W70">
-        <v>-39.0625</v>
+        <v>-37.5</v>
       </c>
       <c r="X70">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="Y70">
         <v>-39.0625</v>
@@ -16672,10 +16675,10 @@
         <v>1.32E-3</v>
       </c>
       <c r="W71">
-        <v>-40.625</v>
+        <v>-39.0625</v>
       </c>
       <c r="X71">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="Y71">
         <v>-40.625</v>
@@ -16920,7 +16923,7 @@
         <v>1.31E-3</v>
       </c>
       <c r="W72">
-        <v>-42.1875</v>
+        <v>-40.625</v>
       </c>
       <c r="X72">
         <v>1.31E-3</v>
@@ -17168,7 +17171,7 @@
         <v>1.31E-3</v>
       </c>
       <c r="W73">
-        <v>-43.75</v>
+        <v>-42.1875</v>
       </c>
       <c r="X73">
         <v>1.31E-3</v>
@@ -17416,7 +17419,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="W74">
-        <v>-45.3125</v>
+        <v>-43.75</v>
       </c>
       <c r="X74">
         <v>1.31E-3</v>
@@ -17664,7 +17667,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="W75">
-        <v>-46.875</v>
+        <v>-45.3125</v>
       </c>
       <c r="X75">
         <v>1.31E-3</v>
@@ -17912,7 +17915,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="W76">
-        <v>-48.4375</v>
+        <v>-46.875</v>
       </c>
       <c r="X76">
         <v>1.31E-3</v>
@@ -18160,10 +18163,10 @@
         <v>1.34E-3</v>
       </c>
       <c r="W77">
-        <v>-50</v>
+        <v>-48.4375</v>
       </c>
       <c r="X77">
-        <v>1.33E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="Y77">
         <v>-50</v>
@@ -18408,7 +18411,7 @@
         <v>1.33E-3</v>
       </c>
       <c r="W78">
-        <v>-51.5625</v>
+        <v>-50</v>
       </c>
       <c r="X78">
         <v>1.33E-3</v>
@@ -18656,10 +18659,10 @@
         <v>1.32E-3</v>
       </c>
       <c r="W79">
-        <v>-53.125</v>
+        <v>-51.5625</v>
       </c>
       <c r="X79">
-        <v>1.31E-3</v>
+        <v>1.3600000000000001E-3</v>
       </c>
       <c r="Y79">
         <v>-53.125</v>
@@ -18904,10 +18907,10 @@
         <v>1.32E-3</v>
       </c>
       <c r="W80">
-        <v>-54.6875</v>
+        <v>-53.125</v>
       </c>
       <c r="X80">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="Y80">
         <v>-54.6875</v>
@@ -19152,10 +19155,10 @@
         <v>1.32E-3</v>
       </c>
       <c r="W81">
-        <v>-56.25</v>
+        <v>-54.6875</v>
       </c>
       <c r="X81">
-        <v>1.31E-3</v>
+        <v>1.2800000000000001E-3</v>
       </c>
       <c r="Y81">
         <v>-56.25</v>
@@ -19400,10 +19403,10 @@
         <v>1.32E-3</v>
       </c>
       <c r="W82">
-        <v>-57.8125</v>
+        <v>-56.25</v>
       </c>
       <c r="X82">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="Y82">
         <v>-57.8125</v>
@@ -19642,7 +19645,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="W83">
-        <v>-59.375</v>
+        <v>-57.8125</v>
       </c>
       <c r="X83">
         <v>1.32E-3</v>
@@ -19872,10 +19875,10 @@
         <v>1.32E-3</v>
       </c>
       <c r="W84">
-        <v>-60.9375</v>
+        <v>-59.375</v>
       </c>
       <c r="X84">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="Y84">
         <v>-60.9375</v>
@@ -20038,6 +20041,14 @@
       </c>
       <c r="CD84">
         <v>1.32E-3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="W85">
+        <v>-60.9375</v>
+      </c>
+      <c r="X85">
+        <v>1.31E-3</v>
       </c>
     </row>
   </sheetData>

--- a/Fig.3(e).xlsx
+++ b/Fig.3(e).xlsx
@@ -2849,13 +2849,13 @@
       <c r="AQ15">
         <v>46.875</v>
       </c>
-      <c r="AR15">
+      <c r="AR15" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="AS15">
         <v>46.875</v>
       </c>
-      <c r="AT15">
+      <c r="AT15" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="AU15">
@@ -3085,7 +3085,7 @@
       <c r="AM16">
         <v>45.3125</v>
       </c>
-      <c r="AN16">
+      <c r="AN16" s="1">
         <v>1.32E-3</v>
       </c>
       <c r="AO16">
@@ -3097,19 +3097,19 @@
       <c r="AQ16">
         <v>45.3125</v>
       </c>
-      <c r="AR16">
+      <c r="AR16" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="AS16">
         <v>45.3125</v>
       </c>
-      <c r="AT16">
+      <c r="AT16" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="AU16">
         <v>45.3125</v>
       </c>
-      <c r="AV16">
+      <c r="AV16" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="AW16">
@@ -3321,13 +3321,13 @@
       <c r="AI17">
         <v>43.75</v>
       </c>
-      <c r="AJ17">
+      <c r="AJ17" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="AK17">
         <v>43.75</v>
       </c>
-      <c r="AL17">
+      <c r="AL17" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="AM17">
@@ -3345,7 +3345,7 @@
       <c r="AQ17">
         <v>43.75</v>
       </c>
-      <c r="AR17" s="1">
+      <c r="AR17">
         <v>1.31E-3</v>
       </c>
       <c r="AS17">
@@ -3357,19 +3357,19 @@
       <c r="AU17">
         <v>43.75</v>
       </c>
-      <c r="AV17">
+      <c r="AV17" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="AW17">
         <v>43.75</v>
       </c>
-      <c r="AX17">
+      <c r="AX17" s="1">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="AY17">
+      <c r="AY17" s="1">
         <v>43.75</v>
       </c>
-      <c r="AZ17">
+      <c r="AZ17" s="1">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="BA17">
@@ -3563,25 +3563,25 @@
       <c r="AG18">
         <v>42.1875</v>
       </c>
-      <c r="AH18">
+      <c r="AH18" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="AI18">
         <v>42.1875</v>
       </c>
-      <c r="AJ18">
+      <c r="AJ18" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="AK18">
         <v>42.1875</v>
       </c>
-      <c r="AL18">
+      <c r="AL18" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="AM18">
         <v>42.1875</v>
       </c>
-      <c r="AN18" s="1">
+      <c r="AN18">
         <v>3.5300000000000002E-3</v>
       </c>
       <c r="AO18">
@@ -3593,7 +3593,7 @@
       <c r="AQ18">
         <v>42.1875</v>
       </c>
-      <c r="AR18" s="1">
+      <c r="AR18">
         <v>7.6099999999999996E-3</v>
       </c>
       <c r="AS18">
@@ -3611,13 +3611,13 @@
       <c r="AW18">
         <v>42.1875</v>
       </c>
-      <c r="AX18">
-        <v>1.31E-3</v>
-      </c>
-      <c r="AY18">
+      <c r="AX18" s="1">
+        <v>1.31E-3</v>
+      </c>
+      <c r="AY18" s="1">
         <v>42.1875</v>
       </c>
-      <c r="AZ18">
+      <c r="AZ18" s="1">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="BA18">
@@ -3805,13 +3805,13 @@
       <c r="AE19">
         <v>40.625</v>
       </c>
-      <c r="AF19">
+      <c r="AF19" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="AG19">
         <v>40.625</v>
       </c>
-      <c r="AH19">
+      <c r="AH19" s="1">
         <v>1.32E-3</v>
       </c>
       <c r="AI19">
@@ -3829,7 +3829,7 @@
       <c r="AM19">
         <v>40.625</v>
       </c>
-      <c r="AN19">
+      <c r="AN19" s="1">
         <v>1.7739999999999999E-2</v>
       </c>
       <c r="AO19">
@@ -3841,7 +3841,7 @@
       <c r="AQ19">
         <v>40.625</v>
       </c>
-      <c r="AR19">
+      <c r="AR19" s="1">
         <v>1.77E-2</v>
       </c>
       <c r="AS19">
@@ -3853,7 +3853,7 @@
       <c r="AU19">
         <v>40.625</v>
       </c>
-      <c r="AV19" s="1">
+      <c r="AV19">
         <v>4.9699999999999996E-3</v>
       </c>
       <c r="AW19">
@@ -3871,25 +3871,25 @@
       <c r="BA19">
         <v>40.625</v>
       </c>
-      <c r="BB19">
-        <v>1.31E-3</v>
-      </c>
-      <c r="BC19">
+      <c r="BB19" s="1">
+        <v>1.31E-3</v>
+      </c>
+      <c r="BC19" s="1">
         <v>40.625</v>
       </c>
-      <c r="BD19">
-        <v>1.31E-3</v>
-      </c>
-      <c r="BE19">
+      <c r="BD19" s="1">
+        <v>1.31E-3</v>
+      </c>
+      <c r="BE19" s="1">
         <v>40.625</v>
       </c>
-      <c r="BF19">
-        <v>1.31E-3</v>
-      </c>
-      <c r="BG19">
+      <c r="BF19" s="1">
+        <v>1.31E-3</v>
+      </c>
+      <c r="BG19" s="1">
         <v>40.625</v>
       </c>
-      <c r="BH19">
+      <c r="BH19" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="BI19">
@@ -4047,13 +4047,13 @@
       <c r="AC20">
         <v>39.0625</v>
       </c>
-      <c r="AD20">
-        <v>1.32E-3</v>
-      </c>
-      <c r="AE20">
+      <c r="AD20" s="1">
+        <v>1.32E-3</v>
+      </c>
+      <c r="AE20" s="1">
         <v>39.0625</v>
       </c>
-      <c r="AF20">
+      <c r="AF20" s="1">
         <v>1.6199999999999999E-3</v>
       </c>
       <c r="AG20">
@@ -4119,25 +4119,25 @@
       <c r="BA20">
         <v>39.0625</v>
       </c>
-      <c r="BB20">
-        <v>1.31E-3</v>
-      </c>
-      <c r="BC20">
+      <c r="BB20" s="1">
+        <v>1.31E-3</v>
+      </c>
+      <c r="BC20" s="1">
         <v>39.0625</v>
       </c>
-      <c r="BD20">
-        <v>1.31E-3</v>
-      </c>
-      <c r="BE20">
+      <c r="BD20" s="1">
+        <v>1.31E-3</v>
+      </c>
+      <c r="BE20" s="1">
         <v>39.0625</v>
       </c>
-      <c r="BF20">
-        <v>1.31E-3</v>
-      </c>
-      <c r="BG20">
+      <c r="BF20" s="1">
+        <v>1.31E-3</v>
+      </c>
+      <c r="BG20" s="1">
         <v>39.0625</v>
       </c>
-      <c r="BH20">
+      <c r="BH20" s="1">
         <v>1.32E-3</v>
       </c>
       <c r="BI20">
@@ -4274,10 +4274,10 @@
       <c r="V21">
         <v>1.32E-3</v>
       </c>
-      <c r="W21">
+      <c r="W21" s="1">
         <v>37.5</v>
       </c>
-      <c r="X21">
+      <c r="X21" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="Y21">
@@ -4289,16 +4289,16 @@
       <c r="AA21">
         <v>37.5</v>
       </c>
-      <c r="AB21">
+      <c r="AB21" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="AC21">
         <v>37.5</v>
       </c>
-      <c r="AD21">
-        <v>1.32E-3</v>
-      </c>
-      <c r="AE21">
+      <c r="AD21" s="1">
+        <v>1.32E-3</v>
+      </c>
+      <c r="AE21" s="1">
         <v>37.5</v>
       </c>
       <c r="AF21" s="1">
@@ -4349,7 +4349,7 @@
       <c r="AU21">
         <v>37.5</v>
       </c>
-      <c r="AV21">
+      <c r="AV21" s="1">
         <v>1.273E-2</v>
       </c>
       <c r="AW21">
@@ -4522,10 +4522,10 @@
       <c r="V22">
         <v>1.32E-3</v>
       </c>
-      <c r="W22">
+      <c r="W22" s="1">
         <v>35.9375</v>
       </c>
-      <c r="X22">
+      <c r="X22" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="Y22">
@@ -4543,10 +4543,10 @@
       <c r="AC22">
         <v>35.9375</v>
       </c>
-      <c r="AD22" s="1">
+      <c r="AD22">
         <v>5.1399999999999996E-3</v>
       </c>
-      <c r="AE22" s="1">
+      <c r="AE22">
         <v>35.9375</v>
       </c>
       <c r="AF22" s="1">
@@ -4639,13 +4639,13 @@
       <c r="BI22">
         <v>35.9375</v>
       </c>
-      <c r="BJ22">
-        <v>1.31E-3</v>
-      </c>
-      <c r="BK22">
+      <c r="BJ22" s="1">
+        <v>1.31E-3</v>
+      </c>
+      <c r="BK22" s="1">
         <v>35.9375</v>
       </c>
-      <c r="BL22">
+      <c r="BL22" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="BM22">
@@ -4767,7 +4767,7 @@
       <c r="U23">
         <v>34.375</v>
       </c>
-      <c r="V23">
+      <c r="V23" s="1">
         <v>1.32E-3</v>
       </c>
       <c r="W23" s="1">
@@ -4776,13 +4776,13 @@
       <c r="X23" s="1">
         <v>1.31E-3</v>
       </c>
-      <c r="Y23">
+      <c r="Y23" s="1">
         <v>34.375</v>
       </c>
-      <c r="Z23">
+      <c r="Z23" s="1">
         <v>1.7799999999999999E-3</v>
       </c>
-      <c r="AA23">
+      <c r="AA23" s="1">
         <v>34.375</v>
       </c>
       <c r="AB23" s="1">
@@ -4794,7 +4794,7 @@
       <c r="AD23" s="1">
         <v>1.511E-2</v>
       </c>
-      <c r="AE23" s="1">
+      <c r="AE23">
         <v>34.375</v>
       </c>
       <c r="AF23" s="1">
@@ -4887,13 +4887,13 @@
       <c r="BI23">
         <v>34.375</v>
       </c>
-      <c r="BJ23">
-        <v>1.31E-3</v>
-      </c>
-      <c r="BK23">
+      <c r="BJ23" s="1">
+        <v>1.31E-3</v>
+      </c>
+      <c r="BK23" s="1">
         <v>34.375</v>
       </c>
-      <c r="BL23">
+      <c r="BL23" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="BM23">
@@ -5015,31 +5015,31 @@
       <c r="U24">
         <v>32.8125</v>
       </c>
-      <c r="V24">
-        <v>1.31E-3</v>
-      </c>
-      <c r="W24" s="1">
+      <c r="V24" s="1">
+        <v>1.31E-3</v>
+      </c>
+      <c r="W24">
         <v>32.8125</v>
       </c>
-      <c r="X24" s="1">
-        <v>1.31E-3</v>
-      </c>
-      <c r="Y24">
+      <c r="X24">
+        <v>1.31E-3</v>
+      </c>
+      <c r="Y24" s="1">
         <v>32.8125</v>
       </c>
-      <c r="Z24">
+      <c r="Z24" s="1">
         <v>2.7000000000000001E-3</v>
       </c>
-      <c r="AA24">
+      <c r="AA24" s="1">
         <v>32.8125</v>
       </c>
-      <c r="AB24">
+      <c r="AB24" s="1">
         <v>1.418E-2</v>
       </c>
       <c r="AC24">
         <v>32.8125</v>
       </c>
-      <c r="AD24">
+      <c r="AD24" s="1">
         <v>1.065E-2</v>
       </c>
       <c r="AE24">
@@ -5069,7 +5069,7 @@
       <c r="AM24">
         <v>32.8125</v>
       </c>
-      <c r="AN24">
+      <c r="AN24" s="1">
         <v>0</v>
       </c>
       <c r="AO24">
@@ -5147,13 +5147,13 @@
       <c r="BM24">
         <v>32.8125</v>
       </c>
-      <c r="BN24">
-        <v>1.31E-3</v>
-      </c>
-      <c r="BO24">
+      <c r="BN24" s="1">
+        <v>1.31E-3</v>
+      </c>
+      <c r="BO24" s="1">
         <v>32.8125</v>
       </c>
-      <c r="BP24">
+      <c r="BP24" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="BQ24">
@@ -5257,7 +5257,7 @@
       <c r="S25">
         <v>31.25</v>
       </c>
-      <c r="T25">
+      <c r="T25" s="1">
         <v>1.5399999999999999E-3</v>
       </c>
       <c r="U25">
@@ -5266,10 +5266,10 @@
       <c r="V25" s="1">
         <v>5.0200000000000002E-3</v>
       </c>
-      <c r="W25" s="1">
+      <c r="W25">
         <v>31.25</v>
       </c>
-      <c r="X25" s="1">
+      <c r="X25">
         <v>3.5599999999999998E-3</v>
       </c>
       <c r="Y25" s="1">
@@ -5347,13 +5347,13 @@
       <c r="AW25">
         <v>31.25</v>
       </c>
-      <c r="AX25" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY25" s="1">
+      <c r="AX25">
+        <v>0</v>
+      </c>
+      <c r="AY25">
         <v>31.25</v>
       </c>
-      <c r="AZ25" s="1">
+      <c r="AZ25">
         <v>0</v>
       </c>
       <c r="BA25">
@@ -5378,7 +5378,7 @@
         <v>31.25</v>
       </c>
       <c r="BH25" s="1">
-        <v>5.1999999999999998E-3</v>
+        <v>7.5599999999999999E-3</v>
       </c>
       <c r="BI25">
         <v>31.25</v>
@@ -5395,13 +5395,13 @@
       <c r="BM25">
         <v>31.25</v>
       </c>
-      <c r="BN25">
-        <v>1.31E-3</v>
-      </c>
-      <c r="BO25">
+      <c r="BN25" s="1">
+        <v>1.31E-3</v>
+      </c>
+      <c r="BO25" s="1">
         <v>31.25</v>
       </c>
-      <c r="BP25">
+      <c r="BP25" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="BQ25">
@@ -5499,13 +5499,13 @@
       <c r="Q26">
         <v>29.6875</v>
       </c>
-      <c r="R26">
-        <v>1.32E-3</v>
-      </c>
-      <c r="S26">
+      <c r="R26" s="1">
+        <v>1.32E-3</v>
+      </c>
+      <c r="S26" s="1">
         <v>29.6875</v>
       </c>
-      <c r="T26">
+      <c r="T26" s="1">
         <v>1.7600000000000001E-3</v>
       </c>
       <c r="U26">
@@ -5517,16 +5517,16 @@
       <c r="W26">
         <v>29.6875</v>
       </c>
-      <c r="X26">
+      <c r="X26" s="1">
         <v>1.3089999999999999E-2</v>
       </c>
-      <c r="Y26" s="1">
+      <c r="Y26">
         <v>29.6875</v>
       </c>
       <c r="Z26" s="1">
         <v>1.15E-2</v>
       </c>
-      <c r="AA26" s="1">
+      <c r="AA26">
         <v>29.6875</v>
       </c>
       <c r="AB26" s="1">
@@ -5598,7 +5598,7 @@
       <c r="AX26" s="1">
         <v>0</v>
       </c>
-      <c r="AY26" s="1">
+      <c r="AY26">
         <v>29.6875</v>
       </c>
       <c r="AZ26" s="1">
@@ -5626,7 +5626,7 @@
         <v>29.6875</v>
       </c>
       <c r="BH26" s="1">
-        <v>1.3089999999999999E-2</v>
+        <v>1.308E-2</v>
       </c>
       <c r="BI26">
         <v>29.6875</v>
@@ -5634,10 +5634,10 @@
       <c r="BJ26" s="1">
         <v>1.3089999999999999E-2</v>
       </c>
-      <c r="BK26" s="1">
+      <c r="BK26">
         <v>29.6875</v>
       </c>
-      <c r="BL26" s="1">
+      <c r="BL26">
         <v>1.7600000000000001E-3</v>
       </c>
       <c r="BM26">
@@ -5747,10 +5747,10 @@
       <c r="Q27">
         <v>28.125</v>
       </c>
-      <c r="R27">
+      <c r="R27" s="1">
         <v>2.2300000000000002E-3</v>
       </c>
-      <c r="S27">
+      <c r="S27" s="1">
         <v>28.125</v>
       </c>
       <c r="T27" s="1">
@@ -5765,10 +5765,10 @@
       <c r="W27">
         <v>28.125</v>
       </c>
-      <c r="X27">
+      <c r="X27" s="1">
         <v>1.0200000000000001E-2</v>
       </c>
-      <c r="Y27" s="1">
+      <c r="Y27">
         <v>28.125</v>
       </c>
       <c r="Z27" s="1">
@@ -5789,7 +5789,7 @@
       <c r="AE27">
         <v>28.125</v>
       </c>
-      <c r="AF27">
+      <c r="AF27" s="1">
         <v>0</v>
       </c>
       <c r="AG27">
@@ -5807,13 +5807,13 @@
       <c r="AK27">
         <v>28.125</v>
       </c>
-      <c r="AL27">
+      <c r="AL27" s="1">
         <v>0</v>
       </c>
       <c r="AM27">
         <v>28.125</v>
       </c>
-      <c r="AN27">
+      <c r="AN27" s="1">
         <v>0</v>
       </c>
       <c r="AO27">
@@ -5843,13 +5843,13 @@
       <c r="AW27">
         <v>28.125</v>
       </c>
-      <c r="AX27">
+      <c r="AX27" s="1">
         <v>0</v>
       </c>
       <c r="AY27">
         <v>28.125</v>
       </c>
-      <c r="AZ27">
+      <c r="AZ27" s="1">
         <v>0</v>
       </c>
       <c r="BA27">
@@ -5874,7 +5874,7 @@
         <v>28.125</v>
       </c>
       <c r="BH27" s="1">
-        <v>8.5599999999999999E-3</v>
+        <v>5.96E-3</v>
       </c>
       <c r="BI27">
         <v>28.125</v>
@@ -5882,10 +5882,10 @@
       <c r="BJ27" s="1">
         <v>8.5599999999999999E-3</v>
       </c>
-      <c r="BK27" s="1">
+      <c r="BK27">
         <v>28.125</v>
       </c>
-      <c r="BL27" s="1">
+      <c r="BL27">
         <v>1.91E-3</v>
       </c>
       <c r="BM27">
@@ -5983,13 +5983,13 @@
       <c r="M28">
         <v>26.5625</v>
       </c>
-      <c r="N28">
-        <v>1.32E-3</v>
-      </c>
-      <c r="O28">
+      <c r="N28" s="1">
+        <v>1.32E-3</v>
+      </c>
+      <c r="O28" s="1">
         <v>26.5625</v>
       </c>
-      <c r="P28">
+      <c r="P28" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="Q28">
@@ -6061,7 +6061,7 @@
       <c r="AM28">
         <v>26.5625</v>
       </c>
-      <c r="AN28" s="1">
+      <c r="AN28">
         <v>0</v>
       </c>
       <c r="AO28">
@@ -6103,26 +6103,26 @@
       <c r="BA28">
         <v>26.5625</v>
       </c>
-      <c r="BB28" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC28" s="1">
+      <c r="BB28">
+        <v>0</v>
+      </c>
+      <c r="BC28">
         <v>26.5625</v>
       </c>
-      <c r="BD28" s="1">
-        <v>0</v>
-      </c>
-      <c r="BE28" s="1">
+      <c r="BD28">
+        <v>0</v>
+      </c>
+      <c r="BE28">
         <v>26.5625</v>
       </c>
       <c r="BF28" s="1">
         <v>1.62003E-7</v>
       </c>
-      <c r="BG28" s="1">
+      <c r="BG28">
         <v>26.5625</v>
       </c>
       <c r="BH28" s="1">
-        <v>2.5015400000000001E-5</v>
+        <v>3.2645699999999998E-5</v>
       </c>
       <c r="BI28">
         <v>26.5625</v>
@@ -6133,7 +6133,7 @@
       <c r="BK28">
         <v>26.5625</v>
       </c>
-      <c r="BL28">
+      <c r="BL28" s="1">
         <v>1.136E-2</v>
       </c>
       <c r="BM28">
@@ -6151,13 +6151,13 @@
       <c r="BQ28">
         <v>26.5625</v>
       </c>
-      <c r="BR28">
-        <v>1.31E-3</v>
-      </c>
-      <c r="BS28">
+      <c r="BR28" s="1">
+        <v>1.31E-3</v>
+      </c>
+      <c r="BS28" s="1">
         <v>26.5625</v>
       </c>
-      <c r="BT28">
+      <c r="BT28" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="BU28">
@@ -6225,19 +6225,19 @@
       <c r="K29">
         <v>25</v>
       </c>
-      <c r="L29">
+      <c r="L29" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="M29">
         <v>25</v>
       </c>
-      <c r="N29">
-        <v>1.31E-3</v>
-      </c>
-      <c r="O29">
+      <c r="N29" s="1">
+        <v>1.31E-3</v>
+      </c>
+      <c r="O29" s="1">
         <v>25</v>
       </c>
-      <c r="P29">
+      <c r="P29" s="1">
         <v>2.2499999999999998E-3</v>
       </c>
       <c r="Q29">
@@ -6246,10 +6246,10 @@
       <c r="R29" s="1">
         <v>1.0240000000000001E-2</v>
       </c>
-      <c r="S29" s="1">
+      <c r="S29">
         <v>25</v>
       </c>
-      <c r="T29" s="1">
+      <c r="T29">
         <v>1.009E-2</v>
       </c>
       <c r="U29">
@@ -6270,10 +6270,10 @@
       <c r="Z29" s="1">
         <v>-5.3429000000000001E-6</v>
       </c>
-      <c r="AA29" s="1">
+      <c r="AA29">
         <v>25</v>
       </c>
-      <c r="AB29" s="1">
+      <c r="AB29">
         <v>0</v>
       </c>
       <c r="AC29">
@@ -6291,7 +6291,7 @@
       <c r="AG29">
         <v>25</v>
       </c>
-      <c r="AH29">
+      <c r="AH29" s="1">
         <v>0</v>
       </c>
       <c r="AI29">
@@ -6370,7 +6370,7 @@
         <v>25</v>
       </c>
       <c r="BH29" s="1">
-        <v>1.0720899999999999E-5</v>
+        <v>2.5353700000000002E-4</v>
       </c>
       <c r="BI29">
         <v>25</v>
@@ -6399,13 +6399,13 @@
       <c r="BQ29">
         <v>25</v>
       </c>
-      <c r="BR29">
-        <v>1.31E-3</v>
-      </c>
-      <c r="BS29">
+      <c r="BR29" s="1">
+        <v>1.31E-3</v>
+      </c>
+      <c r="BS29" s="1">
         <v>25</v>
       </c>
-      <c r="BT29">
+      <c r="BT29" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="BU29">
@@ -6473,7 +6473,7 @@
       <c r="K30">
         <v>23.4375</v>
       </c>
-      <c r="L30">
+      <c r="L30" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="M30">
@@ -6494,10 +6494,10 @@
       <c r="R30" s="1">
         <v>1.79075E-4</v>
       </c>
-      <c r="S30" s="1">
+      <c r="S30">
         <v>23.4375</v>
       </c>
-      <c r="T30" s="1">
+      <c r="T30">
         <v>0</v>
       </c>
       <c r="U30">
@@ -6518,10 +6518,10 @@
       <c r="Z30" s="1">
         <v>3.0940099999999998E-6</v>
       </c>
-      <c r="AA30">
+      <c r="AA30" s="1">
         <v>23.4375</v>
       </c>
-      <c r="AB30">
+      <c r="AB30" s="1">
         <v>0</v>
       </c>
       <c r="AC30">
@@ -6551,13 +6551,13 @@
       <c r="AK30">
         <v>23.4375</v>
       </c>
-      <c r="AL30">
+      <c r="AL30" s="1">
         <v>0</v>
       </c>
       <c r="AM30">
         <v>23.4375</v>
       </c>
-      <c r="AN30">
+      <c r="AN30" s="1">
         <v>0</v>
       </c>
       <c r="AO30">
@@ -6599,26 +6599,26 @@
       <c r="BA30">
         <v>23.4375</v>
       </c>
-      <c r="BB30">
-        <v>0</v>
-      </c>
-      <c r="BC30">
+      <c r="BB30" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC30" s="1">
         <v>23.4375</v>
       </c>
-      <c r="BD30">
-        <v>0</v>
-      </c>
-      <c r="BE30">
+      <c r="BD30" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE30" s="1">
         <v>23.4375</v>
       </c>
-      <c r="BF30">
-        <v>0</v>
-      </c>
-      <c r="BG30">
+      <c r="BF30" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG30" s="1">
         <v>23.4375</v>
       </c>
       <c r="BH30" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5738899999999999E-6</v>
       </c>
       <c r="BI30">
         <v>23.4375</v>
@@ -6659,13 +6659,13 @@
       <c r="BU30">
         <v>23.4375</v>
       </c>
-      <c r="BV30">
-        <v>1.31E-3</v>
-      </c>
-      <c r="BW30">
+      <c r="BV30" s="1">
+        <v>1.31E-3</v>
+      </c>
+      <c r="BW30" s="1">
         <v>23.4375</v>
       </c>
-      <c r="BX30">
+      <c r="BX30" s="1">
         <v>1.31E-3</v>
       </c>
       <c r="BY30">
@@ -6715,10 +6715,10 @@
       <c r="I31">
         <v>21.875</v>
       </c>
-      <c r="J31">
-        <v>1.32E-3</v>
-      </c>
-      <c r="K31">
+      <c r="J31" s="1">
+        <v>1.32E-3</v>
+      </c>
+      <c r="K31" s="1">
         <v>21.875</v>
       </c>
       <c r="L31" s="1">
@@ -6787,7 +6787,7 @@
       <c r="AG31">
         <v>21.875</v>
       </c>
-      <c r="AH31" s="1">
+      <c r="AH31">
         <v>0</v>
       </c>
       <c r="AI31">
@@ -6847,25 +6847,25 @@
       <c r="BA31">
         <v>21.875</v>
       </c>
-      <c r="BB31" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC31" s="1">
+      <c r="BB31">
+        <v>0</v>
+      </c>
+      <c r="BC31">
         <v>21.875</v>
       </c>
-      <c r="BD31" s="1">
-        <v>0</v>
-      </c>
-      <c r="BE31" s="1">
+      <c r="BD31">
+        <v>0</v>
+      </c>
+      <c r="BE31">
         <v>21.875</v>
       </c>
-      <c r="BF31" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG31" s="1">
+      <c r="BF31">
+        <v>0</v>
+      </c>
+      <c r="BG31">
         <v>21.875</v>
       </c>
-      <c r="BH31" s="1">
+      <c r="BH31">
         <v>0</v>
       </c>
       <c r="BI31">
@@ -6907,13 +6907,13 @@
       <c r="BU31">
         <v>21.875</v>
       </c>
-      <c r="BV31">
-        <v>1.32E-3</v>
-      </c>
-      <c r="BW31">
+      <c r="BV31" s="1">
+        <v>1.32E-3</v>
+      </c>
+      <c r="BW31" s="1">
         <v>21.875</v>
       </c>
-      <c r="BX31">
+      <c r="BX31" s="1">
         <v>1.32E-3</v>
       </c>
       <c r="BY31">
@@ -6963,10 +6963,10 @@
       <c r="I32">
         <v>20.3125</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="1">
         <v>1.5499999999999999E-3</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="1">
         <v>20.3125</v>
       </c>
       <c r="L32" s="1">
@@ -7014,7 +7014,7 @@
       <c r="Z32" s="1">
         <v>3.5580000000000001E-6</v>
       </c>
-      <c r="AA32" s="1">
+      <c r="AA32">
         <v>20.3125</v>
       </c>
       <c r="AB32" s="1">
@@ -7035,7 +7035,7 @@
       <c r="AG32">
         <v>20.3125</v>
       </c>
-      <c r="AH32">
+      <c r="AH32" s="1">
         <v>0</v>
       </c>
       <c r="AI32">
@@ -7098,22 +7098,22 @@
       <c r="BB32" s="1">
         <v>3.57363E-6</v>
       </c>
-      <c r="BC32" s="1">
+      <c r="BC32">
         <v>20.3125</v>
       </c>
       <c r="BD32" s="1">
         <v>3.57363E-6</v>
       </c>
-      <c r="BE32" s="1">
+      <c r="BE32">
         <v>20.3125</v>
       </c>
       <c r="BF32" s="1">
         <v>3.5735600000000001E-6</v>
       </c>
-      <c r="BG32" s="1">
+      <c r="BG32">
         <v>20.3125</v>
       </c>
-      <c r="BH32" s="1">
+      <c r="BH32">
         <v>0</v>
       </c>
       <c r="BI32">
@@ -7205,7 +7205,7 @@
       <c r="G33">
         <v>18.75</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="1">
         <v>1.4300000000000001E-3</v>
       </c>
       <c r="I33">
@@ -7226,7 +7226,7 @@
       <c r="N33" s="1">
         <v>2.39433E-4</v>
       </c>
-      <c r="O33" s="1">
+      <c r="O33">
         <v>18.75</v>
       </c>
       <c r="P33" s="1">
@@ -7265,7 +7265,7 @@
       <c r="AA33">
         <v>18.75</v>
       </c>
-      <c r="AB33">
+      <c r="AB33" s="1">
         <v>0</v>
       </c>
       <c r="AC33">
@@ -7283,7 +7283,7 @@
       <c r="AG33">
         <v>18.75</v>
       </c>
-      <c r="AH33">
+      <c r="AH33" s="1">
         <v>0</v>
       </c>
       <c r="AI33">
@@ -7295,13 +7295,13 @@
       <c r="AK33">
         <v>18.75</v>
       </c>
-      <c r="AL33">
+      <c r="AL33" s="1">
         <v>0</v>
       </c>
       <c r="AM33">
         <v>18.75</v>
       </c>
-      <c r="AN33">
+      <c r="AN33" s="1">
         <v>0</v>
       </c>
       <c r="AO33">
@@ -7343,19 +7343,19 @@
       <c r="BA33">
         <v>18.75</v>
       </c>
-      <c r="BB33">
+      <c r="BB33" s="1">
         <v>0</v>
       </c>
       <c r="BC33">
         <v>18.75</v>
       </c>
-      <c r="BD33">
+      <c r="BD33" s="1">
         <v>0</v>
       </c>
       <c r="BE33">
         <v>18.75</v>
       </c>
-      <c r="BF33">
+      <c r="BF33" s="1">
         <v>0</v>
       </c>
       <c r="BG33">
@@ -7453,7 +7453,7 @@
       <c r="G34">
         <v>17.1875</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="1">
         <v>1.41E-3</v>
       </c>
       <c r="I34">
@@ -7474,7 +7474,7 @@
       <c r="N34" s="1">
         <v>4.64572E-5</v>
       </c>
-      <c r="O34" s="1">
+      <c r="O34">
         <v>17.1875</v>
       </c>
       <c r="P34" s="1">
@@ -7549,7 +7549,7 @@
       <c r="AM34">
         <v>17.1875</v>
       </c>
-      <c r="AN34" s="1">
+      <c r="AN34">
         <v>0</v>
       </c>
       <c r="AO34">
@@ -7779,7 +7779,7 @@
       <c r="AG35">
         <v>15.625</v>
       </c>
-      <c r="AH35" s="1">
+      <c r="AH35">
         <v>0</v>
       </c>
       <c r="AI35">
@@ -7890,7 +7890,7 @@
       <c r="BR35" s="1">
         <v>1.7868099999999999E-5</v>
       </c>
-      <c r="BS35" s="1">
+      <c r="BS35">
         <v>14.0625</v>
       </c>
       <c r="BT35" s="1">
@@ -7943,10 +7943,10 @@
       <c r="E36">
         <v>14.0625</v>
       </c>
-      <c r="F36">
-        <v>1.32E-3</v>
-      </c>
-      <c r="G36">
+      <c r="F36" s="1">
+        <v>1.32E-3</v>
+      </c>
+      <c r="G36" s="1">
         <v>14.0625</v>
       </c>
       <c r="H36" s="1">
@@ -8027,7 +8027,7 @@
       <c r="AG36">
         <v>14.0625</v>
       </c>
-      <c r="AH36">
+      <c r="AH36" s="1">
         <v>0</v>
       </c>
       <c r="AI36">
@@ -8039,7 +8039,7 @@
       <c r="AK36">
         <v>14.0625</v>
       </c>
-      <c r="AL36">
+      <c r="AL36" s="1">
         <v>0</v>
       </c>
       <c r="AM36">
@@ -8159,13 +8159,13 @@
       <c r="BY36">
         <v>14.0625</v>
       </c>
-      <c r="BZ36">
-        <v>1.32E-3</v>
-      </c>
-      <c r="CA36">
+      <c r="BZ36" s="1">
+        <v>1.32E-3</v>
+      </c>
+      <c r="CA36" s="1">
         <v>14.0625</v>
       </c>
-      <c r="CB36">
+      <c r="CB36" s="1">
         <v>1.32E-3</v>
       </c>
       <c r="CC36">
@@ -8191,10 +8191,10 @@
       <c r="E37">
         <v>12.5</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="1">
         <v>1.4499999999999999E-3</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="1">
         <v>11.86</v>
       </c>
       <c r="H37" s="1">
@@ -8206,7 +8206,7 @@
       <c r="J37" s="1">
         <v>2.1452499999999998E-5</v>
       </c>
-      <c r="K37" s="1">
+      <c r="K37">
         <v>10.9375</v>
       </c>
       <c r="L37" s="1">
@@ -8221,7 +8221,7 @@
       <c r="O37">
         <v>12.5</v>
       </c>
-      <c r="P37">
+      <c r="P37" s="1">
         <v>0</v>
       </c>
       <c r="Q37">
@@ -8383,7 +8383,7 @@
       <c r="BQ37">
         <v>12.5</v>
       </c>
-      <c r="BR37">
+      <c r="BR37" s="1">
         <v>0</v>
       </c>
       <c r="BS37">
@@ -8407,13 +8407,13 @@
       <c r="BY37">
         <v>12.5</v>
       </c>
-      <c r="BZ37">
+      <c r="BZ37" s="1">
         <v>1.42E-3</v>
       </c>
-      <c r="CA37">
+      <c r="CA37" s="1">
         <v>12.5</v>
       </c>
-      <c r="CB37">
+      <c r="CB37" s="1">
         <v>1.4300000000000001E-3</v>
       </c>
       <c r="CC37">
@@ -8454,7 +8454,7 @@
       <c r="J38" s="1">
         <v>7.1508299999999998E-6</v>
       </c>
-      <c r="K38" s="1">
+      <c r="K38">
         <v>9.375</v>
       </c>
       <c r="L38" s="1">
@@ -8490,10 +8490,10 @@
       <c r="V38">
         <v>0</v>
       </c>
-      <c r="W38">
+      <c r="W38" s="1">
         <v>10.9375</v>
       </c>
-      <c r="X38">
+      <c r="X38" s="1">
         <v>0</v>
       </c>
       <c r="Y38">
@@ -8681,7 +8681,7 @@
       <c r="C39">
         <v>9.375</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="1">
         <v>1.7700000000000001E-3</v>
       </c>
       <c r="E39">
@@ -8738,10 +8738,10 @@
       <c r="V39">
         <v>0</v>
       </c>
-      <c r="W39">
+      <c r="W39" s="1">
         <v>9.375</v>
       </c>
-      <c r="X39">
+      <c r="X39" s="1">
         <v>0</v>
       </c>
       <c r="Y39">
@@ -8882,7 +8882,7 @@
       <c r="BR39" s="1">
         <v>3.57363E-6</v>
       </c>
-      <c r="BS39">
+      <c r="BS39" s="1">
         <v>7.8125</v>
       </c>
       <c r="BT39" s="1">
@@ -8929,7 +8929,7 @@
       <c r="C40">
         <v>7.8125</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="1">
         <v>1.7099999999999999E-3</v>
       </c>
       <c r="E40">
@@ -8965,7 +8965,7 @@
       <c r="O40">
         <v>7.8125</v>
       </c>
-      <c r="P40" s="1">
+      <c r="P40">
         <v>0</v>
       </c>
       <c r="Q40">
@@ -8986,22 +8986,22 @@
       <c r="V40">
         <v>0</v>
       </c>
-      <c r="W40" s="1">
+      <c r="W40">
         <v>7.8125</v>
       </c>
-      <c r="X40" s="1">
+      <c r="X40">
         <v>0</v>
       </c>
       <c r="Y40">
         <v>7.8125</v>
       </c>
-      <c r="Z40">
-        <v>0</v>
-      </c>
-      <c r="AA40">
+      <c r="Z40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="1">
         <v>7.8125</v>
       </c>
-      <c r="AB40">
+      <c r="AB40" s="1">
         <v>0</v>
       </c>
       <c r="AC40">
@@ -9085,19 +9085,19 @@
       <c r="BC40">
         <v>7.8125</v>
       </c>
-      <c r="BD40">
+      <c r="BD40" s="1">
         <v>0</v>
       </c>
       <c r="BE40">
         <v>7.8125</v>
       </c>
-      <c r="BF40">
-        <v>0</v>
-      </c>
-      <c r="BG40">
+      <c r="BF40" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG40" s="1">
         <v>7.8125</v>
       </c>
-      <c r="BH40">
+      <c r="BH40" s="1">
         <v>0</v>
       </c>
       <c r="BI40">
@@ -9127,10 +9127,10 @@
       <c r="BQ40">
         <v>7.8125</v>
       </c>
-      <c r="BR40" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS40" s="1">
+      <c r="BR40">
+        <v>0</v>
+      </c>
+      <c r="BS40">
         <v>6.25</v>
       </c>
       <c r="BT40" s="1">
@@ -9177,7 +9177,7 @@
       <c r="C41">
         <v>6.25</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D41">
         <v>1.6100000000000001E-3</v>
       </c>
       <c r="E41">
@@ -9195,13 +9195,13 @@
       <c r="I41">
         <v>4.6875</v>
       </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41">
+      <c r="J41" s="1">
+        <v>0</v>
+      </c>
+      <c r="K41" s="1">
         <v>4.6875</v>
       </c>
-      <c r="L41">
+      <c r="L41" s="1">
         <v>0</v>
       </c>
       <c r="M41">
@@ -9222,34 +9222,34 @@
       <c r="R41">
         <v>0</v>
       </c>
-      <c r="S41">
+      <c r="S41" s="1">
         <v>6.25</v>
       </c>
-      <c r="T41">
+      <c r="T41" s="1">
         <v>0</v>
       </c>
       <c r="U41">
         <v>6.25</v>
       </c>
-      <c r="V41">
-        <v>0</v>
-      </c>
-      <c r="W41" s="1">
+      <c r="V41" s="1">
+        <v>0</v>
+      </c>
+      <c r="W41">
         <v>6.25</v>
       </c>
-      <c r="X41" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y41">
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="1">
         <v>6.25</v>
       </c>
-      <c r="Z41">
-        <v>0</v>
-      </c>
-      <c r="AA41">
+      <c r="Z41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="1">
         <v>6.25</v>
       </c>
-      <c r="AB41">
+      <c r="AB41" s="1">
         <v>0</v>
       </c>
       <c r="AC41">
@@ -9309,43 +9309,43 @@
       <c r="AU41">
         <v>6.25</v>
       </c>
-      <c r="AV41">
+      <c r="AV41" s="1">
         <v>0</v>
       </c>
       <c r="AW41">
         <v>6.25</v>
       </c>
-      <c r="AX41">
-        <v>0</v>
-      </c>
-      <c r="AY41">
+      <c r="AX41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY41" s="1">
         <v>6.25</v>
       </c>
-      <c r="AZ41">
+      <c r="AZ41" s="1">
         <v>0</v>
       </c>
       <c r="BA41">
         <v>6.25</v>
       </c>
-      <c r="BB41">
-        <v>0</v>
-      </c>
-      <c r="BC41">
+      <c r="BB41" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC41" s="1">
         <v>6.25</v>
       </c>
-      <c r="BD41">
-        <v>0</v>
-      </c>
-      <c r="BE41">
+      <c r="BD41" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE41" s="1">
         <v>6.25</v>
       </c>
-      <c r="BF41">
-        <v>0</v>
-      </c>
-      <c r="BG41">
+      <c r="BF41" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG41" s="1">
         <v>6.25</v>
       </c>
-      <c r="BH41">
+      <c r="BH41" s="1">
         <v>0</v>
       </c>
       <c r="BI41">
@@ -9434,7 +9434,7 @@
       <c r="F42" s="1">
         <v>2.1799100000000001E-4</v>
       </c>
-      <c r="G42" s="1">
+      <c r="G42">
         <v>4.6875</v>
       </c>
       <c r="H42" s="1">
@@ -9443,13 +9443,13 @@
       <c r="I42">
         <v>3.125</v>
       </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
+      <c r="J42" s="1">
+        <v>0</v>
+      </c>
+      <c r="K42" s="1">
         <v>3.125</v>
       </c>
-      <c r="L42">
+      <c r="L42" s="1">
         <v>0</v>
       </c>
       <c r="M42">
@@ -9461,25 +9461,25 @@
       <c r="O42">
         <v>4.6875</v>
       </c>
-      <c r="P42">
+      <c r="P42" s="1">
         <v>0</v>
       </c>
       <c r="Q42">
         <v>4.6875</v>
       </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
+      <c r="R42" s="1">
+        <v>0</v>
+      </c>
+      <c r="S42" s="1">
         <v>4.6875</v>
       </c>
-      <c r="T42">
+      <c r="T42" s="1">
         <v>0</v>
       </c>
       <c r="U42">
         <v>4.6875</v>
       </c>
-      <c r="V42">
+      <c r="V42" s="1">
         <v>0</v>
       </c>
       <c r="W42">
@@ -9488,7 +9488,7 @@
       <c r="X42">
         <v>0</v>
       </c>
-      <c r="Y42">
+      <c r="Y42" s="1">
         <v>4.6875</v>
       </c>
       <c r="Z42" s="1">
@@ -9557,34 +9557,34 @@
       <c r="AU42">
         <v>4.6875</v>
       </c>
-      <c r="AV42">
+      <c r="AV42" s="1">
         <v>0</v>
       </c>
       <c r="AW42">
         <v>4.6875</v>
       </c>
-      <c r="AX42">
-        <v>0</v>
-      </c>
-      <c r="AY42">
+      <c r="AX42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY42" s="1">
         <v>4.6875</v>
       </c>
-      <c r="AZ42">
+      <c r="AZ42" s="1">
         <v>0</v>
       </c>
       <c r="BA42">
         <v>4.6875</v>
       </c>
-      <c r="BB42">
-        <v>0</v>
-      </c>
-      <c r="BC42">
+      <c r="BB42" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC42" s="1">
         <v>4.6875</v>
       </c>
       <c r="BD42" s="1">
         <v>0</v>
       </c>
-      <c r="BE42">
+      <c r="BE42" s="1">
         <v>4.6875</v>
       </c>
       <c r="BF42" s="1">
@@ -9623,19 +9623,19 @@
       <c r="BQ42">
         <v>4.6875</v>
       </c>
-      <c r="BR42">
-        <v>0</v>
-      </c>
-      <c r="BS42">
+      <c r="BR42" s="1">
+        <v>0</v>
+      </c>
+      <c r="BS42" s="1">
         <v>3.125</v>
       </c>
-      <c r="BT42">
+      <c r="BT42" s="1">
         <v>0</v>
       </c>
       <c r="BU42">
         <v>3.125</v>
       </c>
-      <c r="BV42">
+      <c r="BV42" s="1">
         <v>0</v>
       </c>
       <c r="BW42" s="1">
@@ -9673,7 +9673,7 @@
       <c r="C43">
         <v>3.125</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="1">
         <v>1.01E-3</v>
       </c>
       <c r="E43">
@@ -9682,7 +9682,7 @@
       <c r="F43" s="1">
         <v>1.0006200000000001E-4</v>
       </c>
-      <c r="G43" s="1">
+      <c r="G43">
         <v>3.125</v>
       </c>
       <c r="H43" s="1">
@@ -9706,7 +9706,7 @@
       <c r="N43">
         <v>0</v>
       </c>
-      <c r="O43">
+      <c r="O43" s="1">
         <v>3.125</v>
       </c>
       <c r="P43" s="1">
@@ -9715,19 +9715,19 @@
       <c r="Q43">
         <v>3.125</v>
       </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43" s="1">
+      <c r="R43" s="1">
+        <v>0</v>
+      </c>
+      <c r="S43">
         <v>3.125</v>
       </c>
-      <c r="T43" s="1">
+      <c r="T43">
         <v>0</v>
       </c>
       <c r="U43">
         <v>3.125</v>
       </c>
-      <c r="V43" s="1">
+      <c r="V43">
         <v>0</v>
       </c>
       <c r="W43">
@@ -9736,7 +9736,7 @@
       <c r="X43">
         <v>0</v>
       </c>
-      <c r="Y43" s="1">
+      <c r="Y43">
         <v>3.125</v>
       </c>
       <c r="Z43" s="1">
@@ -9951,10 +9951,10 @@
       <c r="M44">
         <v>1.5625</v>
       </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44">
+      <c r="N44" s="1">
+        <v>0</v>
+      </c>
+      <c r="O44" s="1">
         <v>1.5625</v>
       </c>
       <c r="P44" s="1">
@@ -9963,13 +9963,13 @@
       <c r="Q44">
         <v>1.5625</v>
       </c>
-      <c r="R44" s="1">
-        <v>0</v>
-      </c>
-      <c r="S44" s="1">
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
         <v>1.5625</v>
       </c>
-      <c r="T44" s="1">
+      <c r="T44">
         <v>0</v>
       </c>
       <c r="U44">
@@ -9984,7 +9984,7 @@
       <c r="X44">
         <v>0</v>
       </c>
-      <c r="Y44" s="1">
+      <c r="Y44">
         <v>1.5625</v>
       </c>
       <c r="Z44" s="1">
@@ -10005,7 +10005,7 @@
       <c r="AE44">
         <v>1.5625</v>
       </c>
-      <c r="AF44">
+      <c r="AF44" s="1">
         <v>0</v>
       </c>
       <c r="AG44">
@@ -10146,7 +10146,7 @@
       <c r="BZ44" s="1">
         <v>3.5736199999999998E-5</v>
       </c>
-      <c r="CA44" s="1">
+      <c r="CA44">
         <v>1.5625</v>
       </c>
       <c r="CB44" s="1">
@@ -10199,7 +10199,7 @@
       <c r="M45">
         <v>0</v>
       </c>
-      <c r="N45">
+      <c r="N45" s="1">
         <v>0</v>
       </c>
       <c r="O45" s="1">
@@ -10223,14 +10223,14 @@
       <c r="U45">
         <v>0</v>
       </c>
-      <c r="V45">
+      <c r="V45" s="1">
         <v>0</v>
       </c>
       <c r="W45">
         <v>0</v>
       </c>
-      <c r="X45" t="s">
-        <v>2</v>
+      <c r="X45">
+        <v>0</v>
       </c>
       <c r="Y45">
         <v>0</v>
@@ -10238,7 +10238,7 @@
       <c r="Z45" s="1">
         <v>0</v>
       </c>
-      <c r="AA45" s="1">
+      <c r="AA45">
         <v>0</v>
       </c>
       <c r="AB45" s="1">
@@ -10334,11 +10334,11 @@
       <c r="BF45" s="1">
         <v>-3.5735600000000001E-6</v>
       </c>
-      <c r="BG45" s="1">
-        <v>0</v>
-      </c>
-      <c r="BH45" s="1">
-        <v>0</v>
+      <c r="BG45">
+        <v>0</v>
+      </c>
+      <c r="BH45" t="s">
+        <v>2</v>
       </c>
       <c r="BI45">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       <c r="BV45" s="1">
         <v>3.57363E-6</v>
       </c>
-      <c r="BW45" s="1">
+      <c r="BW45">
         <v>0</v>
       </c>
       <c r="BX45" s="1">
@@ -10394,7 +10394,7 @@
       <c r="BZ45" s="1">
         <v>0</v>
       </c>
-      <c r="CA45" s="1">
+      <c r="CA45">
         <v>0</v>
       </c>
       <c r="CB45" s="1">
@@ -10459,7 +10459,7 @@
       <c r="Q46">
         <v>-1.5625</v>
       </c>
-      <c r="R46">
+      <c r="R46" s="1">
         <v>0</v>
       </c>
       <c r="S46">
@@ -10475,18 +10475,18 @@
         <v>3.57363E-6</v>
       </c>
       <c r="W46">
-        <v>0</v>
-      </c>
-      <c r="X46" t="s">
-        <v>2</v>
+        <v>-1.5625</v>
+      </c>
+      <c r="X46" s="1">
+        <v>0</v>
       </c>
       <c r="Y46">
         <v>-1.5625</v>
       </c>
-      <c r="Z46" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="1">
+      <c r="Z46">
+        <v>0</v>
+      </c>
+      <c r="AA46">
         <v>-1.5625</v>
       </c>
       <c r="AB46" s="1">
@@ -10570,23 +10570,23 @@
       <c r="BB46" s="1">
         <v>0</v>
       </c>
-      <c r="BC46" s="1">
+      <c r="BC46">
         <v>-1.5625</v>
       </c>
       <c r="BD46" s="1">
         <v>-3.57363E-6</v>
       </c>
-      <c r="BE46" s="1">
+      <c r="BE46">
         <v>-1.5625</v>
       </c>
       <c r="BF46" s="1">
         <v>-3.5735600000000001E-6</v>
       </c>
-      <c r="BG46" s="1">
-        <v>-1.5625</v>
-      </c>
-      <c r="BH46" s="1">
-        <v>0</v>
+      <c r="BG46">
+        <v>0</v>
+      </c>
+      <c r="BH46" t="s">
+        <v>2</v>
       </c>
       <c r="BI46">
         <v>-1.5625</v>
@@ -10630,7 +10630,7 @@
       <c r="BV46" s="1">
         <v>1.7868099999999999E-5</v>
       </c>
-      <c r="BW46" s="1">
+      <c r="BW46">
         <v>-1.5625</v>
       </c>
       <c r="BX46" s="1">
@@ -10686,7 +10686,7 @@
       <c r="J47" s="1">
         <v>4.2904999999999997E-5</v>
       </c>
-      <c r="K47" s="1">
+      <c r="K47">
         <v>-4.6875</v>
       </c>
       <c r="L47" s="1">
@@ -10710,10 +10710,10 @@
       <c r="R47" s="1">
         <v>3.57363E-6</v>
       </c>
-      <c r="S47">
+      <c r="S47" s="1">
         <v>-3.125</v>
       </c>
-      <c r="T47">
+      <c r="T47" s="1">
         <v>0</v>
       </c>
       <c r="U47">
@@ -10722,10 +10722,10 @@
       <c r="V47" s="1">
         <v>3.57363E-6</v>
       </c>
-      <c r="W47">
-        <v>-1.5625</v>
-      </c>
-      <c r="X47">
+      <c r="W47" s="1">
+        <v>-3.125</v>
+      </c>
+      <c r="X47" s="1">
         <v>0</v>
       </c>
       <c r="Y47">
@@ -10737,7 +10737,7 @@
       <c r="AA47">
         <v>-3.125</v>
       </c>
-      <c r="AB47">
+      <c r="AB47" s="1">
         <v>0</v>
       </c>
       <c r="AC47">
@@ -10749,7 +10749,7 @@
       <c r="AE47">
         <v>-3.125</v>
       </c>
-      <c r="AF47">
+      <c r="AF47" s="1">
         <v>0</v>
       </c>
       <c r="AG47">
@@ -10818,20 +10818,20 @@
       <c r="BB47" s="1">
         <v>0</v>
       </c>
-      <c r="BC47" s="1">
+      <c r="BC47">
         <v>-3.125</v>
       </c>
       <c r="BD47" s="1">
         <v>0</v>
       </c>
-      <c r="BE47" s="1">
+      <c r="BE47">
         <v>-3.125</v>
       </c>
       <c r="BF47" s="1">
         <v>0</v>
       </c>
       <c r="BG47">
-        <v>-3.125</v>
+        <v>-1.5625</v>
       </c>
       <c r="BH47">
         <v>0</v>
@@ -10934,7 +10934,7 @@
       <c r="J48" s="1">
         <v>-4.3330200000000001E-5</v>
       </c>
-      <c r="K48" s="1">
+      <c r="K48">
         <v>-6.25</v>
       </c>
       <c r="L48" s="1">
@@ -10946,7 +10946,7 @@
       <c r="N48" s="1">
         <v>0</v>
       </c>
-      <c r="O48" s="1">
+      <c r="O48">
         <v>-4.6875</v>
       </c>
       <c r="P48" s="1">
@@ -10958,10 +10958,10 @@
       <c r="R48" s="1">
         <v>3.57363E-6</v>
       </c>
-      <c r="S48">
+      <c r="S48" s="1">
         <v>-4.6875</v>
       </c>
-      <c r="T48">
+      <c r="T48" s="1">
         <v>0</v>
       </c>
       <c r="U48">
@@ -10970,10 +10970,10 @@
       <c r="V48">
         <v>0</v>
       </c>
-      <c r="W48">
-        <v>-3.125</v>
-      </c>
-      <c r="X48">
+      <c r="W48" s="1">
+        <v>-4.6875</v>
+      </c>
+      <c r="X48" s="1">
         <v>0</v>
       </c>
       <c r="Y48">
@@ -10997,7 +10997,7 @@
       <c r="AE48">
         <v>-4.6875</v>
       </c>
-      <c r="AF48">
+      <c r="AF48" s="1">
         <v>0</v>
       </c>
       <c r="AG48">
@@ -11079,7 +11079,7 @@
         <v>3.5735600000000001E-6</v>
       </c>
       <c r="BG48">
-        <v>-4.6875</v>
+        <v>-3.125</v>
       </c>
       <c r="BH48">
         <v>0</v>
@@ -11090,10 +11090,10 @@
       <c r="BJ48">
         <v>0</v>
       </c>
-      <c r="BK48">
+      <c r="BK48" s="1">
         <v>-4.6875</v>
       </c>
-      <c r="BL48">
+      <c r="BL48" s="1">
         <v>0</v>
       </c>
       <c r="BM48">
@@ -11194,7 +11194,7 @@
       <c r="N49" s="1">
         <v>3.57363E-6</v>
       </c>
-      <c r="O49" s="1">
+      <c r="O49">
         <v>-6.25</v>
       </c>
       <c r="P49" s="1">
@@ -11203,7 +11203,7 @@
       <c r="Q49">
         <v>-6.25</v>
       </c>
-      <c r="R49">
+      <c r="R49" s="1">
         <v>0</v>
       </c>
       <c r="S49" s="1">
@@ -11218,8 +11218,8 @@
       <c r="V49">
         <v>0</v>
       </c>
-      <c r="W49">
-        <v>-4.6875</v>
+      <c r="W49" s="1">
+        <v>-6.25</v>
       </c>
       <c r="X49" s="1">
         <v>0</v>
@@ -11245,7 +11245,7 @@
       <c r="AE49">
         <v>-6.25</v>
       </c>
-      <c r="AF49" s="1">
+      <c r="AF49">
         <v>0</v>
       </c>
       <c r="AG49">
@@ -11302,10 +11302,10 @@
       <c r="AX49" s="1">
         <v>0</v>
       </c>
-      <c r="AY49" s="1">
+      <c r="AY49">
         <v>-6.25</v>
       </c>
-      <c r="AZ49" s="1">
+      <c r="AZ49">
         <v>0</v>
       </c>
       <c r="BA49">
@@ -11327,21 +11327,21 @@
         <v>3.5735600000000001E-6</v>
       </c>
       <c r="BG49">
-        <v>-6.25</v>
-      </c>
-      <c r="BH49">
+        <v>-4.6875</v>
+      </c>
+      <c r="BH49" s="1">
         <v>0</v>
       </c>
       <c r="BI49">
         <v>-6.25</v>
       </c>
-      <c r="BJ49">
-        <v>0</v>
-      </c>
-      <c r="BK49">
+      <c r="BJ49" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK49" s="1">
         <v>-6.25</v>
       </c>
-      <c r="BL49">
+      <c r="BL49" s="1">
         <v>0</v>
       </c>
       <c r="BM49">
@@ -11467,7 +11467,7 @@
         <v>0</v>
       </c>
       <c r="W50" s="1">
-        <v>-6.25</v>
+        <v>-7.8125</v>
       </c>
       <c r="X50" s="1">
         <v>0</v>
@@ -11550,7 +11550,7 @@
       <c r="AX50" s="1">
         <v>0</v>
       </c>
-      <c r="AY50" s="1">
+      <c r="AY50">
         <v>-7.8125</v>
       </c>
       <c r="AZ50" s="1">
@@ -11575,15 +11575,15 @@
         <v>0</v>
       </c>
       <c r="BG50">
-        <v>-7.8125</v>
-      </c>
-      <c r="BH50">
+        <v>-6.25</v>
+      </c>
+      <c r="BH50" s="1">
         <v>0</v>
       </c>
       <c r="BI50">
         <v>-7.8125</v>
       </c>
-      <c r="BJ50">
+      <c r="BJ50" s="1">
         <v>0</v>
       </c>
       <c r="BK50" s="1">
@@ -11610,7 +11610,7 @@
       <c r="BR50" s="1">
         <v>1.0720899999999999E-5</v>
       </c>
-      <c r="BS50" s="1">
+      <c r="BS50">
         <v>-9.375</v>
       </c>
       <c r="BT50" s="1">
@@ -11702,7 +11702,7 @@
       <c r="R51" s="1">
         <v>0</v>
       </c>
-      <c r="S51" s="1">
+      <c r="S51">
         <v>-9.375</v>
       </c>
       <c r="T51" s="1">
@@ -11711,25 +11711,25 @@
       <c r="U51">
         <v>-9.375</v>
       </c>
-      <c r="V51">
-        <v>0</v>
-      </c>
-      <c r="W51" s="1">
-        <v>-7.8125</v>
+      <c r="V51" s="1">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>-9.375</v>
       </c>
       <c r="X51" s="1">
         <v>0</v>
       </c>
-      <c r="Y51">
+      <c r="Y51" s="1">
         <v>-9.375</v>
       </c>
-      <c r="Z51">
-        <v>0</v>
-      </c>
-      <c r="AA51">
+      <c r="Z51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="1">
         <v>-9.375</v>
       </c>
-      <c r="AB51">
+      <c r="AB51" s="1">
         <v>0</v>
       </c>
       <c r="AC51">
@@ -11741,7 +11741,7 @@
       <c r="AE51">
         <v>-9.375</v>
       </c>
-      <c r="AF51">
+      <c r="AF51" s="1">
         <v>0</v>
       </c>
       <c r="AG51">
@@ -11801,7 +11801,7 @@
       <c r="AY51">
         <v>-9.375</v>
       </c>
-      <c r="AZ51">
+      <c r="AZ51" s="1">
         <v>0</v>
       </c>
       <c r="BA51">
@@ -11823,7 +11823,7 @@
         <v>0</v>
       </c>
       <c r="BG51">
-        <v>-9.375</v>
+        <v>-7.8125</v>
       </c>
       <c r="BH51" s="1">
         <v>0</v>
@@ -11846,7 +11846,7 @@
       <c r="BN51" s="1">
         <v>3.57363E-6</v>
       </c>
-      <c r="BO51" s="1">
+      <c r="BO51">
         <v>-9.375</v>
       </c>
       <c r="BP51" s="1">
@@ -11858,7 +11858,7 @@
       <c r="BR51" s="1">
         <v>2.1441799999999999E-5</v>
       </c>
-      <c r="BS51" s="1">
+      <c r="BS51">
         <v>-10.9375</v>
       </c>
       <c r="BT51" s="1">
@@ -11950,7 +11950,7 @@
       <c r="R52" s="1">
         <v>0</v>
       </c>
-      <c r="S52" s="1">
+      <c r="S52">
         <v>-10.9375</v>
       </c>
       <c r="T52" s="1">
@@ -11959,25 +11959,25 @@
       <c r="U52">
         <v>-10.9375</v>
       </c>
-      <c r="V52">
-        <v>0</v>
-      </c>
-      <c r="W52" s="1">
-        <v>-9.375</v>
+      <c r="V52" s="1">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>-10.9375</v>
       </c>
       <c r="X52" s="1">
         <v>0</v>
       </c>
-      <c r="Y52">
+      <c r="Y52" s="1">
         <v>-10.9375</v>
       </c>
-      <c r="Z52">
-        <v>0</v>
-      </c>
-      <c r="AA52">
+      <c r="Z52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="1">
         <v>-10.9375</v>
       </c>
-      <c r="AB52">
+      <c r="AB52" s="1">
         <v>0</v>
       </c>
       <c r="AC52">
@@ -12037,7 +12037,7 @@
       <c r="AU52">
         <v>-10.9375</v>
       </c>
-      <c r="AV52">
+      <c r="AV52" s="1">
         <v>0</v>
       </c>
       <c r="AW52">
@@ -12071,7 +12071,7 @@
         <v>0</v>
       </c>
       <c r="BG52">
-        <v>-10.9375</v>
+        <v>-9.375</v>
       </c>
       <c r="BH52" s="1">
         <v>0</v>
@@ -12094,7 +12094,7 @@
       <c r="BN52" s="1">
         <v>3.57363E-6</v>
       </c>
-      <c r="BO52" s="1">
+      <c r="BO52">
         <v>-10.9375</v>
       </c>
       <c r="BP52" s="1">
@@ -12210,8 +12210,8 @@
       <c r="V53" s="1">
         <v>0</v>
       </c>
-      <c r="W53" s="1">
-        <v>-10.9375</v>
+      <c r="W53">
+        <v>-12.5</v>
       </c>
       <c r="X53" s="1">
         <v>0</v>
@@ -12234,7 +12234,7 @@
       <c r="AD53">
         <v>0</v>
       </c>
-      <c r="AE53">
+      <c r="AE53" s="1">
         <v>-12.5</v>
       </c>
       <c r="AF53" s="1">
@@ -12285,7 +12285,7 @@
       <c r="AU53">
         <v>-12.5</v>
       </c>
-      <c r="AV53">
+      <c r="AV53" s="1">
         <v>0</v>
       </c>
       <c r="AW53">
@@ -12319,7 +12319,7 @@
         <v>0</v>
       </c>
       <c r="BG53">
-        <v>-12.5</v>
+        <v>-10.9375</v>
       </c>
       <c r="BH53" s="1">
         <v>0</v>
@@ -12459,10 +12459,10 @@
         <v>0</v>
       </c>
       <c r="W54">
-        <v>-12.5</v>
+        <v>-14.0625</v>
       </c>
       <c r="X54" s="1">
-        <v>0</v>
+        <v>3.7365799999999998E-6</v>
       </c>
       <c r="Y54" s="1">
         <v>-14.0625</v>
@@ -12479,13 +12479,13 @@
       <c r="AC54">
         <v>-14.0625</v>
       </c>
-      <c r="AD54">
-        <v>0</v>
-      </c>
-      <c r="AE54">
+      <c r="AD54" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="1">
         <v>-14.0625</v>
       </c>
-      <c r="AF54">
+      <c r="AF54" s="1">
         <v>0</v>
       </c>
       <c r="AG54">
@@ -12566,11 +12566,11 @@
       <c r="BF54">
         <v>0</v>
       </c>
-      <c r="BG54">
-        <v>-14.0625</v>
+      <c r="BG54" s="1">
+        <v>-12.5</v>
       </c>
       <c r="BH54" s="1">
-        <v>3.57363E-6</v>
+        <v>0</v>
       </c>
       <c r="BI54">
         <v>-14.0625</v>
@@ -12707,27 +12707,27 @@
         <v>0</v>
       </c>
       <c r="W55">
-        <v>-14.0625</v>
+        <v>-15.625</v>
       </c>
       <c r="X55" s="1">
         <v>3.7365799999999998E-6</v>
       </c>
-      <c r="Y55" s="1">
+      <c r="Y55">
         <v>-15.625</v>
       </c>
-      <c r="Z55" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA55" s="1">
+      <c r="Z55">
+        <v>0</v>
+      </c>
+      <c r="AA55">
         <v>-15.625</v>
       </c>
-      <c r="AB55" s="1">
+      <c r="AB55">
         <v>0</v>
       </c>
       <c r="AC55">
         <v>-15.625</v>
       </c>
-      <c r="AD55">
+      <c r="AD55" s="1">
         <v>0</v>
       </c>
       <c r="AE55" s="1">
@@ -12799,26 +12799,26 @@
       <c r="BA55">
         <v>-15.625</v>
       </c>
-      <c r="BB55">
-        <v>0</v>
-      </c>
-      <c r="BC55">
+      <c r="BB55" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC55" s="1">
         <v>-15.625</v>
       </c>
-      <c r="BD55">
-        <v>0</v>
-      </c>
-      <c r="BE55">
+      <c r="BD55" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE55" s="1">
         <v>-15.625</v>
       </c>
-      <c r="BF55">
-        <v>0</v>
-      </c>
-      <c r="BG55">
-        <v>-15.625</v>
+      <c r="BF55" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG55" s="1">
+        <v>-14.0625</v>
       </c>
       <c r="BH55" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5738899999999999E-6</v>
       </c>
       <c r="BI55">
         <v>-15.625</v>
@@ -12939,7 +12939,7 @@
       <c r="Q56">
         <v>-17.1875</v>
       </c>
-      <c r="R56" s="1">
+      <c r="R56">
         <v>3.2599999999999999E-3</v>
       </c>
       <c r="S56">
@@ -12955,21 +12955,21 @@
         <v>3.57363E-6</v>
       </c>
       <c r="W56">
-        <v>-15.625</v>
+        <v>-17.1875</v>
       </c>
       <c r="X56" s="1">
         <v>3.7365799999999998E-6</v>
       </c>
-      <c r="Y56" s="1">
+      <c r="Y56">
         <v>-17.1875</v>
       </c>
-      <c r="Z56" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA56" s="1">
+      <c r="Z56">
+        <v>0</v>
+      </c>
+      <c r="AA56">
         <v>-17.1875</v>
       </c>
-      <c r="AB56" s="1">
+      <c r="AB56">
         <v>0</v>
       </c>
       <c r="AC56">
@@ -13047,26 +13047,26 @@
       <c r="BA56">
         <v>-17.1875</v>
       </c>
-      <c r="BB56">
-        <v>0</v>
-      </c>
-      <c r="BC56">
+      <c r="BB56" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC56" s="1">
         <v>-17.1875</v>
       </c>
-      <c r="BD56">
-        <v>0</v>
-      </c>
-      <c r="BE56">
+      <c r="BD56" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE56" s="1">
         <v>-17.1875</v>
       </c>
-      <c r="BF56">
+      <c r="BF56" s="1">
         <v>0</v>
       </c>
       <c r="BG56" s="1">
-        <v>-17.1875</v>
+        <v>-15.625</v>
       </c>
       <c r="BH56" s="1">
-        <v>3.57363E-6</v>
+        <v>3.5738899999999999E-6</v>
       </c>
       <c r="BI56">
         <v>-17.1875</v>
@@ -13074,7 +13074,7 @@
       <c r="BJ56" s="1">
         <v>3.57363E-6</v>
       </c>
-      <c r="BK56" s="1">
+      <c r="BK56">
         <v>-17.1875</v>
       </c>
       <c r="BL56" s="1">
@@ -13203,15 +13203,15 @@
         <v>7.1472599999999999E-6</v>
       </c>
       <c r="W57">
-        <v>-17.1875</v>
+        <v>-18.75</v>
       </c>
       <c r="X57" s="1">
-        <v>3.7365799999999998E-6</v>
+        <v>1.12094E-5</v>
       </c>
       <c r="Y57">
         <v>-18.75</v>
       </c>
-      <c r="Z57">
+      <c r="Z57" s="1">
         <v>0</v>
       </c>
       <c r="AA57">
@@ -13226,16 +13226,16 @@
       <c r="AD57" s="1">
         <v>0</v>
       </c>
-      <c r="AE57" s="1">
+      <c r="AE57">
         <v>-18.75</v>
       </c>
-      <c r="AF57" s="1">
+      <c r="AF57">
         <v>0</v>
       </c>
       <c r="AG57">
         <v>-18.75</v>
       </c>
-      <c r="AH57">
+      <c r="AH57" s="1">
         <v>0</v>
       </c>
       <c r="AI57">
@@ -13286,10 +13286,10 @@
       <c r="AX57">
         <v>0</v>
       </c>
-      <c r="AY57">
+      <c r="AY57" s="1">
         <v>-18.75</v>
       </c>
-      <c r="AZ57">
+      <c r="AZ57" s="1">
         <v>0</v>
       </c>
       <c r="BA57">
@@ -13311,10 +13311,10 @@
         <v>0</v>
       </c>
       <c r="BG57" s="1">
-        <v>-18.75</v>
+        <v>-17.1875</v>
       </c>
       <c r="BH57" s="1">
-        <v>1.0720899999999999E-5</v>
+        <v>3.5738899999999999E-6</v>
       </c>
       <c r="BI57">
         <v>-18.75</v>
@@ -13322,7 +13322,7 @@
       <c r="BJ57" s="1">
         <v>1.0720899999999999E-5</v>
       </c>
-      <c r="BK57" s="1">
+      <c r="BK57">
         <v>-18.75</v>
       </c>
       <c r="BL57" s="1">
@@ -13451,10 +13451,10 @@
         <v>1.0720899999999999E-5</v>
       </c>
       <c r="W58">
-        <v>-18.75</v>
+        <v>-20.3125</v>
       </c>
       <c r="X58" s="1">
-        <v>1.12094E-5</v>
+        <v>4.0786199999999999E-5</v>
       </c>
       <c r="Y58">
         <v>-20.3125</v>
@@ -13474,7 +13474,7 @@
       <c r="AD58" s="1">
         <v>0</v>
       </c>
-      <c r="AE58" s="1">
+      <c r="AE58">
         <v>-20.3125</v>
       </c>
       <c r="AF58" s="1">
@@ -13483,7 +13483,7 @@
       <c r="AG58">
         <v>-20.3125</v>
       </c>
-      <c r="AH58">
+      <c r="AH58" s="1">
         <v>0</v>
       </c>
       <c r="AI58">
@@ -13531,13 +13531,13 @@
       <c r="AW58">
         <v>-20.3125</v>
       </c>
-      <c r="AX58">
-        <v>0</v>
-      </c>
-      <c r="AY58">
+      <c r="AX58" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY58" s="1">
         <v>-20.3125</v>
       </c>
-      <c r="AZ58">
+      <c r="AZ58" s="1">
         <v>0</v>
       </c>
       <c r="BA58">
@@ -13558,11 +13558,11 @@
       <c r="BF58" s="1">
         <v>0</v>
       </c>
-      <c r="BG58" s="1">
-        <v>-20.3125</v>
+      <c r="BG58">
+        <v>-18.75</v>
       </c>
       <c r="BH58" s="1">
-        <v>2.5015300000000001E-5</v>
+        <v>1.0721600000000001E-5</v>
       </c>
       <c r="BI58">
         <v>-20.3125</v>
@@ -13699,10 +13699,10 @@
         <v>3.9309800000000001E-5</v>
       </c>
       <c r="W59">
-        <v>-20.3125</v>
+        <v>-21.875</v>
       </c>
       <c r="X59" s="1">
-        <v>4.0786199999999999E-5</v>
+        <v>3.1650499999999999E-6</v>
       </c>
       <c r="Y59">
         <v>-21.875</v>
@@ -13737,7 +13737,7 @@
       <c r="AI59">
         <v>-21.875</v>
       </c>
-      <c r="AJ59">
+      <c r="AJ59" s="1">
         <v>0</v>
       </c>
       <c r="AK59">
@@ -13779,7 +13779,7 @@
       <c r="AW59">
         <v>-21.875</v>
       </c>
-      <c r="AX59">
+      <c r="AX59" s="1">
         <v>0</v>
       </c>
       <c r="AY59" s="1">
@@ -13794,23 +13794,23 @@
       <c r="BB59" s="1">
         <v>0</v>
       </c>
-      <c r="BC59" s="1">
+      <c r="BC59">
         <v>-21.875</v>
       </c>
-      <c r="BD59" s="1">
-        <v>0</v>
-      </c>
-      <c r="BE59" s="1">
+      <c r="BD59">
+        <v>0</v>
+      </c>
+      <c r="BE59">
         <v>-21.875</v>
       </c>
-      <c r="BF59" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG59" s="1">
-        <v>-21.875</v>
+      <c r="BF59">
+        <v>0</v>
+      </c>
+      <c r="BG59">
+        <v>-20.3125</v>
       </c>
       <c r="BH59" s="1">
-        <v>1.07209E-4</v>
+        <v>2.5017100000000001E-5</v>
       </c>
       <c r="BI59">
         <v>-21.875</v>
@@ -13947,10 +13947,10 @@
         <v>6.6499999999999997E-3</v>
       </c>
       <c r="W60">
-        <v>-21.875</v>
+        <v>-23.4375</v>
       </c>
       <c r="X60" s="1">
-        <v>3.1650499999999999E-6</v>
+        <v>1.8718399999999999E-4</v>
       </c>
       <c r="Y60">
         <v>-23.4375</v>
@@ -13973,7 +13973,7 @@
       <c r="AE60">
         <v>-23.4375</v>
       </c>
-      <c r="AF60" s="1">
+      <c r="AF60">
         <v>0</v>
       </c>
       <c r="AG60">
@@ -13985,7 +13985,7 @@
       <c r="AI60">
         <v>-23.4375</v>
       </c>
-      <c r="AJ60">
+      <c r="AJ60" s="1">
         <v>0</v>
       </c>
       <c r="AK60">
@@ -14030,10 +14030,10 @@
       <c r="AX60" s="1">
         <v>0</v>
       </c>
-      <c r="AY60" s="1">
+      <c r="AY60">
         <v>-23.4375</v>
       </c>
-      <c r="AZ60" s="1">
+      <c r="AZ60">
         <v>0</v>
       </c>
       <c r="BA60">
@@ -14042,23 +14042,23 @@
       <c r="BB60" s="1">
         <v>3.57363E-6</v>
       </c>
-      <c r="BC60" s="1">
+      <c r="BC60">
         <v>-23.4375</v>
       </c>
-      <c r="BD60" s="1">
-        <v>0</v>
-      </c>
-      <c r="BE60" s="1">
+      <c r="BD60">
+        <v>0</v>
+      </c>
+      <c r="BE60">
         <v>-23.4375</v>
       </c>
-      <c r="BF60" s="1">
+      <c r="BF60">
         <v>9.9600000000000001E-3</v>
       </c>
       <c r="BG60">
-        <v>-23.4375</v>
+        <v>-21.875</v>
       </c>
       <c r="BH60" s="1">
-        <v>-3.2162600000000003E-5</v>
+        <v>1.07217E-4</v>
       </c>
       <c r="BI60">
         <v>-23.4375</v>
@@ -14195,10 +14195,10 @@
         <v>1.1129999999999999E-2</v>
       </c>
       <c r="W61">
-        <v>-23.4375</v>
-      </c>
-      <c r="X61" s="1">
-        <v>1.8718399999999999E-4</v>
+        <v>-25</v>
+      </c>
+      <c r="X61">
+        <v>1.1129999999999999E-2</v>
       </c>
       <c r="Y61">
         <v>-25</v>
@@ -14239,13 +14239,13 @@
       <c r="AK61">
         <v>-25</v>
       </c>
-      <c r="AL61">
+      <c r="AL61" s="1">
         <v>0</v>
       </c>
       <c r="AM61">
         <v>-25</v>
       </c>
-      <c r="AN61">
+      <c r="AN61" s="1">
         <v>0</v>
       </c>
       <c r="AO61">
@@ -14257,7 +14257,7 @@
       <c r="AQ61">
         <v>-25</v>
       </c>
-      <c r="AR61">
+      <c r="AR61" s="1">
         <v>0</v>
       </c>
       <c r="AS61">
@@ -14278,7 +14278,7 @@
       <c r="AX61" s="1">
         <v>0</v>
       </c>
-      <c r="AY61" s="1">
+      <c r="AY61">
         <v>-25</v>
       </c>
       <c r="AZ61" s="1">
@@ -14303,10 +14303,10 @@
         <v>1.0670000000000001E-2</v>
       </c>
       <c r="BG61">
-        <v>-25</v>
-      </c>
-      <c r="BH61">
-        <v>1.102E-2</v>
+        <v>-23.4375</v>
+      </c>
+      <c r="BH61" s="1">
+        <v>-3.2164900000000001E-5</v>
       </c>
       <c r="BI61">
         <v>-25</v>
@@ -14443,10 +14443,10 @@
         <v>5.1700000000000001E-3</v>
       </c>
       <c r="W62">
-        <v>-25</v>
+        <v>-26.5625</v>
       </c>
       <c r="X62">
-        <v>1.1129999999999999E-2</v>
+        <v>1.157E-2</v>
       </c>
       <c r="Y62">
         <v>-26.5625</v>
@@ -14505,7 +14505,7 @@
       <c r="AQ62">
         <v>-26.5625</v>
       </c>
-      <c r="AR62">
+      <c r="AR62" s="1">
         <v>0</v>
       </c>
       <c r="AS62">
@@ -14551,10 +14551,10 @@
         <v>1.41E-3</v>
       </c>
       <c r="BG62">
-        <v>-26.5625</v>
+        <v>-25</v>
       </c>
       <c r="BH62">
-        <v>1.18E-2</v>
+        <v>1.102E-2</v>
       </c>
       <c r="BI62">
         <v>-26.5625</v>
@@ -14691,10 +14691,10 @@
         <v>1.32E-3</v>
       </c>
       <c r="W63">
-        <v>-26.5625</v>
+        <v>-28.125</v>
       </c>
       <c r="X63">
-        <v>1.157E-2</v>
+        <v>1.31E-3</v>
       </c>
       <c r="Y63">
         <v>-28.125</v>
@@ -14735,13 +14735,13 @@
       <c r="AK63">
         <v>-28.125</v>
       </c>
-      <c r="AL63" s="1">
+      <c r="AL63">
         <v>0</v>
       </c>
       <c r="AM63">
         <v>-28.125</v>
       </c>
-      <c r="AN63" s="1">
+      <c r="AN63">
         <v>0</v>
       </c>
       <c r="AO63">
@@ -14799,10 +14799,10 @@
         <v>1.58E-3</v>
       </c>
       <c r="BG63">
-        <v>-28.125</v>
+        <v>-26.5625</v>
       </c>
       <c r="BH63">
-        <v>1.31E-3</v>
+        <v>1.18E-2</v>
       </c>
       <c r="BI63">
         <v>-28.125</v>
@@ -14939,7 +14939,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="W64">
-        <v>-28.125</v>
+        <v>-29.6875</v>
       </c>
       <c r="X64">
         <v>1.31E-3</v>
@@ -14983,13 +14983,13 @@
       <c r="AK64">
         <v>-29.6875</v>
       </c>
-      <c r="AL64">
+      <c r="AL64" s="1">
         <v>0</v>
       </c>
       <c r="AM64">
         <v>-29.6875</v>
       </c>
-      <c r="AN64">
+      <c r="AN64" s="1">
         <v>0</v>
       </c>
       <c r="AO64">
@@ -15047,7 +15047,7 @@
         <v>1.74E-3</v>
       </c>
       <c r="BG64">
-        <v>-29.6875</v>
+        <v>-28.125</v>
       </c>
       <c r="BH64">
         <v>1.31E-3</v>
@@ -15187,7 +15187,7 @@
         <v>1.31E-3</v>
       </c>
       <c r="W65">
-        <v>-29.6875</v>
+        <v>-31.25</v>
       </c>
       <c r="X65">
         <v>1.31E-3</v>
@@ -15295,7 +15295,7 @@
         <v>1.5100000000000001E-3</v>
       </c>
       <c r="BG65">
-        <v>-31.25</v>
+        <v>-29.6875</v>
       </c>
       <c r="BH65">
         <v>1.31E-3</v>
@@ -15435,7 +15435,7 @@
         <v>1.31E-3</v>
       </c>
       <c r="W66">
-        <v>-31.25</v>
+        <v>-32.8125</v>
       </c>
       <c r="X66">
         <v>1.31E-3</v>
@@ -15543,7 +15543,7 @@
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="BG66">
-        <v>-32.8125</v>
+        <v>-31.25</v>
       </c>
       <c r="BH66">
         <v>1.31E-3</v>
@@ -15683,7 +15683,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="W67">
-        <v>-32.8125</v>
+        <v>-34.375</v>
       </c>
       <c r="X67">
         <v>1.31E-3</v>
@@ -15791,7 +15791,7 @@
         <v>1.31E-3</v>
       </c>
       <c r="BG67">
-        <v>-34.375</v>
+        <v>-32.8125</v>
       </c>
       <c r="BH67">
         <v>1.31E-3</v>
@@ -15931,7 +15931,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="W68">
-        <v>-34.375</v>
+        <v>-35.9375</v>
       </c>
       <c r="X68">
         <v>1.31E-3</v>
@@ -16039,7 +16039,7 @@
         <v>1.31E-3</v>
       </c>
       <c r="BG68">
-        <v>-35.9375</v>
+        <v>-34.375</v>
       </c>
       <c r="BH68">
         <v>1.31E-3</v>
@@ -16179,7 +16179,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="W69">
-        <v>-35.9375</v>
+        <v>-37.5</v>
       </c>
       <c r="X69">
         <v>1.31E-3</v>
@@ -16287,7 +16287,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="BG69">
-        <v>-37.5</v>
+        <v>-35.9375</v>
       </c>
       <c r="BH69">
         <v>1.31E-3</v>
@@ -16427,10 +16427,10 @@
         <v>1.32E-3</v>
       </c>
       <c r="W70">
-        <v>-37.5</v>
+        <v>-39.0625</v>
       </c>
       <c r="X70">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="Y70">
         <v>-39.0625</v>
@@ -16535,10 +16535,10 @@
         <v>1.32E-3</v>
       </c>
       <c r="BG70">
-        <v>-39.0625</v>
+        <v>-37.5</v>
       </c>
       <c r="BH70">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="BI70">
         <v>-39.0625</v>
@@ -16675,10 +16675,10 @@
         <v>1.32E-3</v>
       </c>
       <c r="W71">
-        <v>-39.0625</v>
+        <v>-40.625</v>
       </c>
       <c r="X71">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="Y71">
         <v>-40.625</v>
@@ -16783,10 +16783,10 @@
         <v>1.31E-3</v>
       </c>
       <c r="BG71">
-        <v>-40.625</v>
+        <v>-39.0625</v>
       </c>
       <c r="BH71">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="BI71">
         <v>-40.625</v>
@@ -16923,7 +16923,7 @@
         <v>1.31E-3</v>
       </c>
       <c r="W72">
-        <v>-40.625</v>
+        <v>-42.1875</v>
       </c>
       <c r="X72">
         <v>1.31E-3</v>
@@ -17031,7 +17031,7 @@
         <v>1.31E-3</v>
       </c>
       <c r="BG72">
-        <v>-42.1875</v>
+        <v>-40.625</v>
       </c>
       <c r="BH72">
         <v>1.31E-3</v>
@@ -17171,7 +17171,7 @@
         <v>1.31E-3</v>
       </c>
       <c r="W73">
-        <v>-42.1875</v>
+        <v>-43.75</v>
       </c>
       <c r="X73">
         <v>1.31E-3</v>
@@ -17279,7 +17279,7 @@
         <v>1.31E-3</v>
       </c>
       <c r="BG73">
-        <v>-43.75</v>
+        <v>-42.1875</v>
       </c>
       <c r="BH73">
         <v>1.31E-3</v>
@@ -17419,7 +17419,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="W74">
-        <v>-43.75</v>
+        <v>-45.3125</v>
       </c>
       <c r="X74">
         <v>1.31E-3</v>
@@ -17527,7 +17527,7 @@
         <v>1.31E-3</v>
       </c>
       <c r="BG74">
-        <v>-45.3125</v>
+        <v>-43.75</v>
       </c>
       <c r="BH74">
         <v>1.31E-3</v>
@@ -17667,7 +17667,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="W75">
-        <v>-45.3125</v>
+        <v>-46.875</v>
       </c>
       <c r="X75">
         <v>1.31E-3</v>
@@ -17775,7 +17775,7 @@
         <v>1.31E-3</v>
       </c>
       <c r="BG75">
-        <v>-46.875</v>
+        <v>-45.3125</v>
       </c>
       <c r="BH75">
         <v>1.31E-3</v>
@@ -17915,7 +17915,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="W76">
-        <v>-46.875</v>
+        <v>-48.4375</v>
       </c>
       <c r="X76">
         <v>1.31E-3</v>
@@ -18023,7 +18023,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="BG76">
-        <v>-48.4375</v>
+        <v>-46.875</v>
       </c>
       <c r="BH76">
         <v>1.31E-3</v>
@@ -18163,10 +18163,10 @@
         <v>1.34E-3</v>
       </c>
       <c r="W77">
-        <v>-48.4375</v>
+        <v>-50</v>
       </c>
       <c r="X77">
-        <v>1.31E-3</v>
+        <v>1.33E-3</v>
       </c>
       <c r="Y77">
         <v>-50</v>
@@ -18271,10 +18271,10 @@
         <v>1.33E-3</v>
       </c>
       <c r="BG77">
-        <v>-50</v>
+        <v>-48.4375</v>
       </c>
       <c r="BH77">
-        <v>1.33E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="BI77">
         <v>-50</v>
@@ -18411,10 +18411,10 @@
         <v>1.33E-3</v>
       </c>
       <c r="W78">
-        <v>-50</v>
+        <v>-51.5625</v>
       </c>
       <c r="X78">
-        <v>1.33E-3</v>
+        <v>1.3600000000000001E-3</v>
       </c>
       <c r="Y78">
         <v>-51.5625</v>
@@ -18519,7 +18519,7 @@
         <v>1.33E-3</v>
       </c>
       <c r="BG78">
-        <v>-51.5625</v>
+        <v>-50</v>
       </c>
       <c r="BH78">
         <v>1.33E-3</v>
@@ -18659,10 +18659,10 @@
         <v>1.32E-3</v>
       </c>
       <c r="W79">
-        <v>-51.5625</v>
+        <v>-53.125</v>
       </c>
       <c r="X79">
-        <v>1.3600000000000001E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="Y79">
         <v>-53.125</v>
@@ -18767,10 +18767,10 @@
         <v>1.31E-3</v>
       </c>
       <c r="BG79">
-        <v>-53.125</v>
+        <v>-51.5625</v>
       </c>
       <c r="BH79">
-        <v>1.31E-3</v>
+        <v>1.33E-3</v>
       </c>
       <c r="BI79">
         <v>-53.125</v>
@@ -18907,10 +18907,10 @@
         <v>1.32E-3</v>
       </c>
       <c r="W80">
-        <v>-53.125</v>
+        <v>-54.6875</v>
       </c>
       <c r="X80">
-        <v>1.31E-3</v>
+        <v>1.2800000000000001E-3</v>
       </c>
       <c r="Y80">
         <v>-54.6875</v>
@@ -19015,10 +19015,10 @@
         <v>1.32E-3</v>
       </c>
       <c r="BG80">
-        <v>-54.6875</v>
+        <v>-53.125</v>
       </c>
       <c r="BH80">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="BI80">
         <v>-54.6875</v>
@@ -19155,10 +19155,10 @@
         <v>1.32E-3</v>
       </c>
       <c r="W81">
-        <v>-54.6875</v>
+        <v>-56.25</v>
       </c>
       <c r="X81">
-        <v>1.2800000000000001E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="Y81">
         <v>-56.25</v>
@@ -19263,10 +19263,10 @@
         <v>1.31E-3</v>
       </c>
       <c r="BG81">
-        <v>-56.25</v>
+        <v>-54.6875</v>
       </c>
       <c r="BH81">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="BI81">
         <v>-56.25</v>
@@ -19403,10 +19403,10 @@
         <v>1.32E-3</v>
       </c>
       <c r="W82">
-        <v>-56.25</v>
+        <v>-57.8125</v>
       </c>
       <c r="X82">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="Y82">
         <v>-57.8125</v>
@@ -19511,10 +19511,10 @@
         <v>1.31E-3</v>
       </c>
       <c r="BG82">
-        <v>-57.8125</v>
+        <v>-56.25</v>
       </c>
       <c r="BH82">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="BI82">
         <v>-57.8125</v>
@@ -19645,7 +19645,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="W83">
-        <v>-57.8125</v>
+        <v>-59.375</v>
       </c>
       <c r="X83">
         <v>1.32E-3</v>
@@ -19753,7 +19753,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="BG83">
-        <v>-59.375</v>
+        <v>-57.8125</v>
       </c>
       <c r="BH83">
         <v>1.32E-3</v>
@@ -19875,10 +19875,10 @@
         <v>1.32E-3</v>
       </c>
       <c r="W84">
-        <v>-59.375</v>
+        <v>-60.9375</v>
       </c>
       <c r="X84">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="Y84">
         <v>-60.9375</v>
@@ -19983,10 +19983,10 @@
         <v>1.32E-3</v>
       </c>
       <c r="BG84">
-        <v>-60.9375</v>
+        <v>-59.375</v>
       </c>
       <c r="BH84">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="BI84">
         <v>-60.9375</v>
@@ -20044,10 +20044,10 @@
       </c>
     </row>
     <row r="85" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="W85">
+      <c r="BG85">
         <v>-60.9375</v>
       </c>
-      <c r="X85">
+      <c r="BH85">
         <v>1.31E-3</v>
       </c>
     </row>

--- a/Fig.3(e).xlsx
+++ b/Fig.3(e).xlsx
@@ -24,15 +24,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>I</t>
   </si>
   <si>
     <t>dV/dI</t>
-  </si>
-  <si>
-    <t>--</t>
   </si>
 </sst>
 </file>
@@ -516,7 +513,7 @@
         <v>60.9375</v>
       </c>
       <c r="J6">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="K6">
         <v>60.9375</v>
@@ -764,7 +761,7 @@
         <v>59.375</v>
       </c>
       <c r="J7">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="K7">
         <v>59.375</v>
@@ -1012,7 +1009,7 @@
         <v>57.8125</v>
       </c>
       <c r="J8">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="K8">
         <v>57.8125</v>
@@ -2004,7 +2001,7 @@
         <v>51.5625</v>
       </c>
       <c r="J12">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="K12">
         <v>51.5625</v>
@@ -2748,7 +2745,7 @@
         <v>46.875</v>
       </c>
       <c r="J15">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="K15">
         <v>46.875</v>
@@ -3492,7 +3489,7 @@
         <v>42.1875</v>
       </c>
       <c r="J18">
-        <v>1.31E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="K18">
         <v>42.1875</v>
@@ -3740,7 +3737,7 @@
         <v>40.625</v>
       </c>
       <c r="J19">
-        <v>1.31E-3</v>
+        <v>1.3699999999999999E-3</v>
       </c>
       <c r="K19">
         <v>40.625</v>
@@ -3988,7 +3985,7 @@
         <v>39.0625</v>
       </c>
       <c r="J20">
-        <v>1.31E-3</v>
+        <v>1.16E-3</v>
       </c>
       <c r="K20">
         <v>39.0625</v>
@@ -4236,7 +4233,7 @@
         <v>37.5</v>
       </c>
       <c r="J21">
-        <v>1.32E-3</v>
+        <v>1.09E-3</v>
       </c>
       <c r="K21">
         <v>37.5</v>
@@ -4484,7 +4481,7 @@
         <v>35.9375</v>
       </c>
       <c r="J22">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="K22">
         <v>35.9375</v>
@@ -5228,7 +5225,7 @@
         <v>31.25</v>
       </c>
       <c r="J25">
-        <v>1.31E-3</v>
+        <v>1.5200000000000001E-3</v>
       </c>
       <c r="K25">
         <v>31.25</v>
@@ -5476,7 +5473,7 @@
         <v>29.6875</v>
       </c>
       <c r="J26">
-        <v>1.31E-3</v>
+        <v>1.5200000000000001E-3</v>
       </c>
       <c r="K26">
         <v>29.6875</v>
@@ -6716,7 +6713,7 @@
         <v>21.875</v>
       </c>
       <c r="J31" s="1">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="K31" s="1">
         <v>21.875</v>
@@ -6964,7 +6961,7 @@
         <v>20.3125</v>
       </c>
       <c r="J32" s="1">
-        <v>1.5499999999999999E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="K32" s="1">
         <v>20.3125</v>
@@ -7212,13 +7209,13 @@
         <v>18.75</v>
       </c>
       <c r="J33" s="1">
-        <v>4.7000000000000002E-3</v>
+        <v>3.9199999999999999E-3</v>
       </c>
       <c r="K33" s="1">
         <v>18.75</v>
       </c>
       <c r="L33" s="1">
-        <v>8.5000000000000006E-3</v>
+        <v>8.4799999999999997E-3</v>
       </c>
       <c r="M33">
         <v>18.75</v>
@@ -7398,13 +7395,13 @@
         <v>18.75</v>
       </c>
       <c r="BT33" s="1">
-        <v>8.43E-3</v>
+        <v>8.4200000000000004E-3</v>
       </c>
       <c r="BU33">
         <v>18.75</v>
       </c>
       <c r="BV33" s="1">
-        <v>4.5199999999999997E-3</v>
+        <v>4.9699999999999996E-3</v>
       </c>
       <c r="BW33" s="1">
         <v>18.75</v>
@@ -7457,16 +7454,16 @@
         <v>1.41E-3</v>
       </c>
       <c r="I34">
-        <v>15.625</v>
+        <v>17.1875</v>
       </c>
       <c r="J34" s="1">
-        <v>3.79E-3</v>
+        <v>7.8399999999999997E-3</v>
       </c>
       <c r="K34" s="1">
-        <v>15.625</v>
+        <v>17.1875</v>
       </c>
       <c r="L34" s="1">
-        <v>9.4821199999999999E-6</v>
+        <v>4.9307000000000001E-5</v>
       </c>
       <c r="M34">
         <v>17.1875</v>
@@ -7643,16 +7640,16 @@
         <v>4.2883599999999997E-5</v>
       </c>
       <c r="BS34" s="1">
-        <v>15.625</v>
+        <v>17.1875</v>
       </c>
       <c r="BT34" s="1">
-        <v>5.8381400000000003E-5</v>
+        <v>4.92972E-5</v>
       </c>
       <c r="BU34">
-        <v>15.625</v>
+        <v>17.1875</v>
       </c>
       <c r="BV34" s="1">
-        <v>3.9699999999999996E-3</v>
+        <v>7.7200000000000003E-3</v>
       </c>
       <c r="BW34" s="1">
         <v>17.1875</v>
@@ -7705,16 +7702,16 @@
         <v>1.3799999999999999E-3</v>
       </c>
       <c r="I35">
-        <v>14.0625</v>
+        <v>15.625</v>
       </c>
       <c r="J35" s="1">
-        <v>3.00282E-6</v>
+        <v>4.5799999999999999E-3</v>
       </c>
       <c r="K35" s="1">
-        <v>14.0625</v>
+        <v>15.625</v>
       </c>
       <c r="L35" s="1">
-        <v>-4.5095099999999996E-6</v>
+        <v>3.18925E-5</v>
       </c>
       <c r="M35">
         <v>15.625</v>
@@ -7891,16 +7888,16 @@
         <v>1.7868099999999999E-5</v>
       </c>
       <c r="BS35">
-        <v>14.0625</v>
+        <v>15.625</v>
       </c>
       <c r="BT35" s="1">
-        <v>6.9469100000000002E-5</v>
+        <v>6.1348500000000004E-5</v>
       </c>
       <c r="BU35">
-        <v>14.0625</v>
+        <v>15.625</v>
       </c>
       <c r="BV35" s="1">
-        <v>1.4294500000000001E-4</v>
+        <v>3.5100000000000001E-3</v>
       </c>
       <c r="BW35" s="1">
         <v>15.625</v>
@@ -7953,16 +7950,16 @@
         <v>4.7999999999999996E-3</v>
       </c>
       <c r="I36">
-        <v>12.5</v>
+        <v>14.0625</v>
       </c>
       <c r="J36" s="1">
-        <v>5.0055800000000003E-5</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>12.5</v>
+        <v>14.0625</v>
       </c>
       <c r="L36" s="1">
-        <v>2.4484000000000001E-5</v>
+        <v>-4.5095099999999996E-6</v>
       </c>
       <c r="M36">
         <v>14.0625</v>
@@ -8139,16 +8136,16 @@
         <v>7.1472599999999999E-6</v>
       </c>
       <c r="BS36" s="1">
-        <v>12.5</v>
+        <v>14.0625</v>
       </c>
       <c r="BT36" s="1">
-        <v>5.0030800000000002E-5</v>
+        <v>6.9469100000000002E-5</v>
       </c>
       <c r="BU36">
-        <v>12.5</v>
+        <v>14.0625</v>
       </c>
       <c r="BV36" s="1">
-        <v>5.0030800000000002E-5</v>
+        <v>1.4294500000000001E-4</v>
       </c>
       <c r="BW36" s="1">
         <v>14.0625</v>
@@ -8201,16 +8198,16 @@
         <v>4.0699999999999998E-3</v>
       </c>
       <c r="I37">
-        <v>10.9375</v>
+        <v>12.5</v>
       </c>
       <c r="J37" s="1">
-        <v>2.1452499999999998E-5</v>
+        <v>0</v>
       </c>
       <c r="K37">
-        <v>10.9375</v>
+        <v>12.5</v>
       </c>
       <c r="L37" s="1">
-        <v>2.1308999999999999E-5</v>
+        <v>2.4484000000000001E-5</v>
       </c>
       <c r="M37">
         <v>12.5</v>
@@ -8387,16 +8384,16 @@
         <v>0</v>
       </c>
       <c r="BS37">
-        <v>10.9375</v>
+        <v>12.5</v>
       </c>
       <c r="BT37" s="1">
-        <v>2.1441799999999999E-5</v>
+        <v>5.0030800000000002E-5</v>
       </c>
       <c r="BU37">
-        <v>10.9375</v>
+        <v>12.5</v>
       </c>
       <c r="BV37" s="1">
-        <v>2.1441799999999999E-5</v>
+        <v>5.0030800000000002E-5</v>
       </c>
       <c r="BW37" s="1">
         <v>11.86</v>
@@ -8449,16 +8446,16 @@
         <v>1.9663499999999999E-5</v>
       </c>
       <c r="I38">
-        <v>9.375</v>
+        <v>10.9375</v>
       </c>
       <c r="J38" s="1">
-        <v>7.1508299999999998E-6</v>
+        <v>0</v>
       </c>
       <c r="K38">
-        <v>9.375</v>
+        <v>10.9375</v>
       </c>
       <c r="L38" s="1">
-        <v>-1.1111799999999999E-5</v>
+        <v>2.1308999999999999E-5</v>
       </c>
       <c r="M38">
         <v>10.9375</v>
@@ -8635,16 +8632,16 @@
         <v>3.57363E-6</v>
       </c>
       <c r="BS38" s="1">
-        <v>9.375</v>
+        <v>10.9375</v>
       </c>
       <c r="BT38" s="1">
-        <v>7.1472500000000001E-6</v>
+        <v>2.1441799999999999E-5</v>
       </c>
       <c r="BU38">
-        <v>9.375</v>
+        <v>10.9375</v>
       </c>
       <c r="BV38" s="1">
-        <v>7.1472500000000001E-6</v>
+        <v>2.1441799999999999E-5</v>
       </c>
       <c r="BW38" s="1">
         <v>10.9375</v>
@@ -8697,16 +8694,16 @@
         <v>7.1476799999999996E-6</v>
       </c>
       <c r="I39">
-        <v>7.8125</v>
+        <v>9.375</v>
       </c>
       <c r="J39" s="1">
-        <v>3.57541E-6</v>
+        <v>0</v>
       </c>
       <c r="K39">
-        <v>7.8125</v>
+        <v>9.375</v>
       </c>
       <c r="L39" s="1">
-        <v>3.7434200000000002E-6</v>
+        <v>-1.1111799999999999E-5</v>
       </c>
       <c r="M39">
         <v>9.375</v>
@@ -8883,16 +8880,16 @@
         <v>3.57363E-6</v>
       </c>
       <c r="BS39" s="1">
-        <v>7.8125</v>
+        <v>9.375</v>
       </c>
       <c r="BT39" s="1">
-        <v>3.57363E-6</v>
+        <v>7.1472500000000001E-6</v>
       </c>
       <c r="BU39">
-        <v>7.8125</v>
+        <v>9.375</v>
       </c>
       <c r="BV39" s="1">
-        <v>3.57363E-6</v>
+        <v>7.1472599999999999E-6</v>
       </c>
       <c r="BW39" s="1">
         <v>9.375</v>
@@ -8945,16 +8942,16 @@
         <v>3.5738399999999998E-6</v>
       </c>
       <c r="I40">
-        <v>6.25</v>
+        <v>7.8125</v>
       </c>
       <c r="J40" s="1">
-        <v>3.57541E-6</v>
+        <v>0</v>
       </c>
       <c r="K40">
-        <v>6.25</v>
+        <v>7.8125</v>
       </c>
       <c r="L40" s="1">
-        <v>2.2342100000000001E-5</v>
+        <v>3.7434200000000002E-6</v>
       </c>
       <c r="M40">
         <v>7.8125</v>
@@ -9131,13 +9128,13 @@
         <v>0</v>
       </c>
       <c r="BS40">
-        <v>6.25</v>
+        <v>7.8125</v>
       </c>
       <c r="BT40" s="1">
         <v>3.57363E-6</v>
       </c>
       <c r="BU40">
-        <v>6.25</v>
+        <v>7.8125</v>
       </c>
       <c r="BV40" s="1">
         <v>3.57363E-6</v>
@@ -9193,16 +9190,16 @@
         <v>3.5738399999999998E-6</v>
       </c>
       <c r="I41">
-        <v>4.6875</v>
+        <v>6.25</v>
       </c>
       <c r="J41" s="1">
         <v>0</v>
       </c>
       <c r="K41" s="1">
-        <v>4.6875</v>
+        <v>6.25</v>
       </c>
       <c r="L41" s="1">
-        <v>0</v>
+        <v>2.2342100000000001E-5</v>
       </c>
       <c r="M41">
         <v>6.25</v>
@@ -9379,16 +9376,16 @@
         <v>-3.57363E-6</v>
       </c>
       <c r="BS41" s="1">
-        <v>4.6875</v>
+        <v>6.25</v>
       </c>
       <c r="BT41" s="1">
-        <v>0</v>
+        <v>3.57363E-6</v>
       </c>
       <c r="BU41">
-        <v>4.6875</v>
+        <v>6.25</v>
       </c>
       <c r="BV41" s="1">
-        <v>0</v>
+        <v>3.57363E-6</v>
       </c>
       <c r="BW41" s="1">
         <v>6.25</v>
@@ -9441,13 +9438,13 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>3.125</v>
+        <v>4.6875</v>
       </c>
       <c r="J42" s="1">
         <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>3.125</v>
+        <v>4.6875</v>
       </c>
       <c r="L42" s="1">
         <v>0</v>
@@ -9627,13 +9624,13 @@
         <v>0</v>
       </c>
       <c r="BS42" s="1">
-        <v>3.125</v>
+        <v>4.6875</v>
       </c>
       <c r="BT42" s="1">
         <v>0</v>
       </c>
       <c r="BU42">
-        <v>3.125</v>
+        <v>4.6875</v>
       </c>
       <c r="BV42" s="1">
         <v>0</v>
@@ -9689,13 +9686,13 @@
         <v>0</v>
       </c>
       <c r="I43">
-        <v>1.5625</v>
+        <v>3.125</v>
       </c>
       <c r="J43" s="1">
         <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>1.5625</v>
+        <v>3.125</v>
       </c>
       <c r="L43" s="1">
         <v>0</v>
@@ -9875,13 +9872,13 @@
         <v>3.57363E-6</v>
       </c>
       <c r="BS43" s="1">
-        <v>1.5625</v>
+        <v>3.125</v>
       </c>
       <c r="BT43" s="1">
         <v>0</v>
       </c>
       <c r="BU43">
-        <v>1.5625</v>
+        <v>3.125</v>
       </c>
       <c r="BV43" s="1">
         <v>0</v>
@@ -9937,13 +9934,13 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>1.5625</v>
       </c>
       <c r="J44" s="1">
         <v>0</v>
       </c>
       <c r="K44" s="1">
-        <v>0</v>
+        <v>1.5625</v>
       </c>
       <c r="L44" s="1">
         <v>0</v>
@@ -10123,13 +10120,13 @@
         <v>-3.57363E-6</v>
       </c>
       <c r="BS44" s="1">
-        <v>0</v>
+        <v>1.5625</v>
       </c>
       <c r="BT44" s="1">
         <v>0</v>
       </c>
       <c r="BU44">
-        <v>0</v>
+        <v>1.5625</v>
       </c>
       <c r="BV44" s="1">
         <v>0</v>
@@ -10185,16 +10182,16 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>-1.5625</v>
+        <v>0</v>
       </c>
       <c r="J45" s="1">
-        <v>3.57541E-6</v>
+        <v>0</v>
       </c>
       <c r="K45" s="1">
-        <v>-1.5625</v>
+        <v>0</v>
       </c>
       <c r="L45" s="1">
-        <v>3.5423400000000002E-6</v>
+        <v>0</v>
       </c>
       <c r="M45">
         <v>0</v>
@@ -10337,8 +10334,8 @@
       <c r="BG45">
         <v>0</v>
       </c>
-      <c r="BH45" t="s">
-        <v>2</v>
+      <c r="BH45">
+        <v>0</v>
       </c>
       <c r="BI45">
         <v>0</v>
@@ -10371,16 +10368,16 @@
         <v>0</v>
       </c>
       <c r="BS45" s="1">
-        <v>-1.5625</v>
+        <v>0</v>
       </c>
       <c r="BT45" s="1">
-        <v>3.57363E-6</v>
+        <v>0</v>
       </c>
       <c r="BU45">
-        <v>-1.5625</v>
+        <v>0</v>
       </c>
       <c r="BV45" s="1">
-        <v>3.57363E-6</v>
+        <v>0</v>
       </c>
       <c r="BW45">
         <v>0</v>
@@ -10433,16 +10430,16 @@
         <v>3.5738399999999998E-6</v>
       </c>
       <c r="I46">
-        <v>-3.125</v>
+        <v>-1.5625</v>
       </c>
       <c r="J46" s="1">
-        <v>1.7877099999999999E-5</v>
+        <v>0</v>
       </c>
       <c r="K46" s="1">
-        <v>-3.125</v>
+        <v>-1.5625</v>
       </c>
       <c r="L46" s="1">
-        <v>1.7835200000000002E-5</v>
+        <v>3.5423400000000002E-6</v>
       </c>
       <c r="M46">
         <v>-1.5625</v>
@@ -10583,10 +10580,10 @@
         <v>-3.5735600000000001E-6</v>
       </c>
       <c r="BG46">
-        <v>0</v>
-      </c>
-      <c r="BH46" t="s">
-        <v>2</v>
+        <v>-1.5625</v>
+      </c>
+      <c r="BH46">
+        <v>0</v>
       </c>
       <c r="BI46">
         <v>-1.5625</v>
@@ -10619,16 +10616,16 @@
         <v>0</v>
       </c>
       <c r="BS46" s="1">
-        <v>-3.125</v>
+        <v>-1.5625</v>
       </c>
       <c r="BT46" s="1">
-        <v>1.7868099999999999E-5</v>
+        <v>3.57363E-6</v>
       </c>
       <c r="BU46">
-        <v>-3.125</v>
+        <v>-1.5625</v>
       </c>
       <c r="BV46" s="1">
-        <v>1.7868099999999999E-5</v>
+        <v>3.57363E-6</v>
       </c>
       <c r="BW46">
         <v>-1.5625</v>
@@ -10681,16 +10678,16 @@
         <v>1.7869200000000002E-5</v>
       </c>
       <c r="I47">
-        <v>-4.6875</v>
+        <v>-3.125</v>
       </c>
       <c r="J47" s="1">
-        <v>4.2904999999999997E-5</v>
+        <v>0</v>
       </c>
       <c r="K47">
-        <v>-4.6875</v>
+        <v>-3.125</v>
       </c>
       <c r="L47" s="1">
-        <v>4.2924099999999998E-5</v>
+        <v>1.7835200000000002E-5</v>
       </c>
       <c r="M47">
         <v>-3.125</v>
@@ -10831,7 +10828,7 @@
         <v>0</v>
       </c>
       <c r="BG47">
-        <v>-1.5625</v>
+        <v>-3.125</v>
       </c>
       <c r="BH47">
         <v>0</v>
@@ -10867,16 +10864,16 @@
         <v>0</v>
       </c>
       <c r="BS47" s="1">
-        <v>-4.6875</v>
+        <v>-3.125</v>
       </c>
       <c r="BT47" s="1">
-        <v>4.2883499999999997E-5</v>
+        <v>1.7868099999999999E-5</v>
       </c>
       <c r="BU47">
-        <v>-4.6875</v>
+        <v>-3.125</v>
       </c>
       <c r="BV47" s="1">
-        <v>4.2883499999999997E-5</v>
+        <v>1.7868099999999999E-5</v>
       </c>
       <c r="BW47">
         <v>-3.125</v>
@@ -10929,16 +10926,16 @@
         <v>2.8620000000000002E-4</v>
       </c>
       <c r="I48">
-        <v>-6.25</v>
+        <v>-4.6875</v>
       </c>
       <c r="J48" s="1">
-        <v>-4.3330200000000001E-5</v>
+        <v>0</v>
       </c>
       <c r="K48">
-        <v>-6.25</v>
+        <v>-4.6875</v>
       </c>
       <c r="L48" s="1">
-        <v>1.47218E-5</v>
+        <v>4.2924099999999998E-5</v>
       </c>
       <c r="M48">
         <v>-4.6875</v>
@@ -11079,7 +11076,7 @@
         <v>3.5735600000000001E-6</v>
       </c>
       <c r="BG48">
-        <v>-3.125</v>
+        <v>-4.6875</v>
       </c>
       <c r="BH48">
         <v>0</v>
@@ -11115,16 +11112,16 @@
         <v>0</v>
       </c>
       <c r="BS48" s="1">
-        <v>-6.25</v>
+        <v>-4.6875</v>
       </c>
       <c r="BT48" s="1">
-        <v>6.39795E-5</v>
+        <v>4.2883499999999997E-5</v>
       </c>
       <c r="BU48">
-        <v>-6.25</v>
+        <v>-4.6875</v>
       </c>
       <c r="BV48" s="1">
-        <v>8.9340700000000003E-5</v>
+        <v>4.2883599999999997E-5</v>
       </c>
       <c r="BW48">
         <v>-4.6875</v>
@@ -11177,16 +11174,16 @@
         <v>3.1199999999999999E-3</v>
       </c>
       <c r="I49">
-        <v>-7.8125</v>
+        <v>-6.25</v>
       </c>
       <c r="J49" s="1">
-        <v>-4.6480400000000003E-5</v>
+        <v>0</v>
       </c>
       <c r="K49">
-        <v>-7.8125</v>
+        <v>-6.25</v>
       </c>
       <c r="L49" s="1">
-        <v>-1.2013E-5</v>
+        <v>1.47218E-5</v>
       </c>
       <c r="M49">
         <v>-6.25</v>
@@ -11327,7 +11324,7 @@
         <v>3.5735600000000001E-6</v>
       </c>
       <c r="BG49">
-        <v>-4.6875</v>
+        <v>-6.25</v>
       </c>
       <c r="BH49" s="1">
         <v>0</v>
@@ -11363,16 +11360,16 @@
         <v>3.57363E-6</v>
       </c>
       <c r="BS49" s="1">
-        <v>-7.8125</v>
+        <v>-6.25</v>
       </c>
       <c r="BT49" s="1">
-        <v>8.6583700000000002E-5</v>
+        <v>6.39795E-5</v>
       </c>
       <c r="BU49">
-        <v>-7.8125</v>
+        <v>-6.25</v>
       </c>
       <c r="BV49" s="1">
-        <v>1.8582900000000001E-4</v>
+        <v>8.9340799999999997E-5</v>
       </c>
       <c r="BW49">
         <v>-6.25</v>
@@ -11425,16 +11422,16 @@
         <v>3.48E-3</v>
       </c>
       <c r="I50">
-        <v>-9.375</v>
+        <v>-7.8125</v>
       </c>
       <c r="J50" s="1">
-        <v>1.0568099999999999E-4</v>
+        <v>2.14186E-4</v>
       </c>
       <c r="K50">
-        <v>-9.375</v>
+        <v>-7.8125</v>
       </c>
       <c r="L50" s="1">
-        <v>1.6107500000000001E-5</v>
+        <v>-1.2013E-5</v>
       </c>
       <c r="M50">
         <v>-7.8125</v>
@@ -11575,7 +11572,7 @@
         <v>0</v>
       </c>
       <c r="BG50">
-        <v>-6.25</v>
+        <v>-7.8125</v>
       </c>
       <c r="BH50" s="1">
         <v>0</v>
@@ -11611,16 +11608,16 @@
         <v>1.0720899999999999E-5</v>
       </c>
       <c r="BS50">
-        <v>-9.375</v>
+        <v>-7.8125</v>
       </c>
       <c r="BT50" s="1">
-        <v>-3.5390499999999999E-5</v>
+        <v>-5.2350299999999999E-5</v>
       </c>
       <c r="BU50">
-        <v>-9.375</v>
+        <v>-7.8125</v>
       </c>
       <c r="BV50" s="1">
-        <v>5.4676499999999995E-4</v>
+        <v>1.2412999999999999E-4</v>
       </c>
       <c r="BW50">
         <v>-7.8125</v>
@@ -11673,16 +11670,16 @@
         <v>1.5200000000000001E-3</v>
       </c>
       <c r="I51">
-        <v>-10.9375</v>
-      </c>
-      <c r="J51">
-        <v>2.99E-3</v>
+        <v>-9.375</v>
+      </c>
+      <c r="J51" s="1">
+        <v>6.4973400000000001E-4</v>
       </c>
       <c r="K51">
-        <v>-10.9375</v>
+        <v>-9.375</v>
       </c>
       <c r="L51" s="1">
-        <v>2.2757099999999999E-5</v>
+        <v>1.6107500000000001E-5</v>
       </c>
       <c r="M51">
         <v>-9.375</v>
@@ -11823,7 +11820,7 @@
         <v>0</v>
       </c>
       <c r="BG51">
-        <v>-7.8125</v>
+        <v>-9.375</v>
       </c>
       <c r="BH51" s="1">
         <v>0</v>
@@ -11859,16 +11856,16 @@
         <v>2.1441799999999999E-5</v>
       </c>
       <c r="BS51">
-        <v>-10.9375</v>
+        <v>-9.375</v>
       </c>
       <c r="BT51" s="1">
-        <v>-2.5831999999999999E-5</v>
+        <v>-5.5671999999999998E-5</v>
       </c>
       <c r="BU51">
-        <v>-10.9375</v>
-      </c>
-      <c r="BV51">
-        <v>3.0400000000000002E-3</v>
+        <v>-9.375</v>
+      </c>
+      <c r="BV51" s="1">
+        <v>5.45591E-4</v>
       </c>
       <c r="BW51">
         <v>-9.375</v>
@@ -11921,16 +11918,16 @@
         <v>1.4300000000000001E-3</v>
       </c>
       <c r="I52">
-        <v>-14.0625</v>
+        <v>-10.9375</v>
       </c>
       <c r="J52">
-        <v>3.5699999999999998E-3</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="K52">
-        <v>-12.5</v>
+        <v>-10.9375</v>
       </c>
       <c r="L52" s="1">
-        <v>1.58364E-4</v>
+        <v>2.2757099999999999E-5</v>
       </c>
       <c r="M52">
         <v>-10.9375</v>
@@ -12071,7 +12068,7 @@
         <v>0</v>
       </c>
       <c r="BG52">
-        <v>-9.375</v>
+        <v>-10.9375</v>
       </c>
       <c r="BH52" s="1">
         <v>0</v>
@@ -12107,16 +12104,16 @@
         <v>4.6456999999999999E-5</v>
       </c>
       <c r="BS52">
-        <v>-12.5</v>
+        <v>-10.9375</v>
       </c>
       <c r="BT52" s="1">
-        <v>1.8582900000000001E-4</v>
+        <v>3.3595900000000001E-5</v>
       </c>
       <c r="BU52">
-        <v>-14.0625</v>
+        <v>-10.9375</v>
       </c>
       <c r="BV52">
-        <v>3.29E-3</v>
+        <v>3.31E-3</v>
       </c>
       <c r="BW52">
         <v>-10.9375</v>
@@ -12163,22 +12160,22 @@
         <v>1.32E-3</v>
       </c>
       <c r="G53">
-        <v>-11.86</v>
+        <v>-12.5</v>
       </c>
       <c r="H53">
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="I53">
-        <v>-15.625</v>
+        <v>-12.5</v>
       </c>
       <c r="J53">
-        <v>1.33E-3</v>
+        <v>5.2300000000000003E-3</v>
       </c>
       <c r="K53">
-        <v>-14.0625</v>
-      </c>
-      <c r="L53">
-        <v>6.5100000000000002E-3</v>
+        <v>-12.5</v>
+      </c>
+      <c r="L53" s="1">
+        <v>1.58364E-4</v>
       </c>
       <c r="M53">
         <v>-12.5</v>
@@ -12319,7 +12316,7 @@
         <v>0</v>
       </c>
       <c r="BG53">
-        <v>-10.9375</v>
+        <v>-12.5</v>
       </c>
       <c r="BH53" s="1">
         <v>0</v>
@@ -12355,16 +12352,16 @@
         <v>1.14356E-4</v>
       </c>
       <c r="BS53">
-        <v>-14.0625</v>
-      </c>
-      <c r="BT53">
-        <v>6.45E-3</v>
+        <v>-12.5</v>
+      </c>
+      <c r="BT53" s="1">
+        <v>1.2674799999999999E-4</v>
       </c>
       <c r="BU53">
-        <v>-15.625</v>
+        <v>-12.5</v>
       </c>
       <c r="BV53">
-        <v>1.33E-3</v>
+        <v>5.2399999999999999E-3</v>
       </c>
       <c r="BW53">
         <v>-11.86</v>
@@ -12417,16 +12414,16 @@
         <v>1.32E-3</v>
       </c>
       <c r="I54">
-        <v>-17.1875</v>
+        <v>-14.0625</v>
       </c>
       <c r="J54">
-        <v>1.32E-3</v>
+        <v>2.8300000000000001E-3</v>
       </c>
       <c r="K54">
-        <v>-15.625</v>
+        <v>-14.0625</v>
       </c>
       <c r="L54">
-        <v>7.0200000000000002E-3</v>
+        <v>6.5100000000000002E-3</v>
       </c>
       <c r="M54">
         <v>-14.0625</v>
@@ -12567,10 +12564,10 @@
         <v>0</v>
       </c>
       <c r="BG54" s="1">
-        <v>-12.5</v>
+        <v>-14.0625</v>
       </c>
       <c r="BH54" s="1">
-        <v>0</v>
+        <v>3.5738899999999999E-6</v>
       </c>
       <c r="BI54">
         <v>-14.0625</v>
@@ -12603,16 +12600,16 @@
         <v>2.4599999999999999E-3</v>
       </c>
       <c r="BS54">
-        <v>-15.625</v>
+        <v>-14.0625</v>
       </c>
       <c r="BT54">
-        <v>6.9899999999999997E-3</v>
+        <v>6.5300000000000002E-3</v>
       </c>
       <c r="BU54">
-        <v>-17.1875</v>
+        <v>-14.0625</v>
       </c>
       <c r="BV54">
-        <v>1.32E-3</v>
+        <v>3.0799999999999998E-3</v>
       </c>
       <c r="BW54">
         <v>-14.0625</v>
@@ -12665,16 +12662,16 @@
         <v>1.33E-3</v>
       </c>
       <c r="I55">
-        <v>-18.75</v>
+        <v>-15.625</v>
       </c>
       <c r="J55">
-        <v>1.31E-3</v>
+        <v>1.5200000000000001E-3</v>
       </c>
       <c r="K55">
-        <v>-17.1875</v>
+        <v>-15.625</v>
       </c>
       <c r="L55">
-        <v>1.32E-3</v>
+        <v>7.0200000000000002E-3</v>
       </c>
       <c r="M55">
         <v>-15.625</v>
@@ -12815,7 +12812,7 @@
         <v>0</v>
       </c>
       <c r="BG55" s="1">
-        <v>-14.0625</v>
+        <v>-15.625</v>
       </c>
       <c r="BH55" s="1">
         <v>3.5738899999999999E-6</v>
@@ -12851,16 +12848,16 @@
         <v>7.0800000000000004E-3</v>
       </c>
       <c r="BS55">
-        <v>-17.1875</v>
+        <v>-15.625</v>
       </c>
       <c r="BT55">
-        <v>1.32E-3</v>
+        <v>7.0699999999999999E-3</v>
       </c>
       <c r="BU55">
-        <v>-18.75</v>
+        <v>-15.625</v>
       </c>
       <c r="BV55">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="BW55">
         <v>-15.625</v>
@@ -12913,16 +12910,16 @@
         <v>1.32E-3</v>
       </c>
       <c r="I56">
-        <v>-20.3125</v>
+        <v>-17.1875</v>
       </c>
       <c r="J56">
-        <v>1.31E-3</v>
+        <v>1.09E-3</v>
       </c>
       <c r="K56">
-        <v>-18.75</v>
+        <v>-17.1875</v>
       </c>
       <c r="L56">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="M56">
         <v>-17.1875</v>
@@ -13063,7 +13060,7 @@
         <v>0</v>
       </c>
       <c r="BG56" s="1">
-        <v>-15.625</v>
+        <v>-17.1875</v>
       </c>
       <c r="BH56" s="1">
         <v>3.5738899999999999E-6</v>
@@ -13099,16 +13096,16 @@
         <v>5.3600000000000002E-3</v>
       </c>
       <c r="BS56">
-        <v>-18.75</v>
+        <v>-17.1875</v>
       </c>
       <c r="BT56">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="BU56">
-        <v>-20.3125</v>
+        <v>-17.1875</v>
       </c>
       <c r="BV56">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="BW56">
         <v>-17.1875</v>
@@ -13161,13 +13158,13 @@
         <v>1.31E-3</v>
       </c>
       <c r="I57">
-        <v>-21.875</v>
+        <v>-18.75</v>
       </c>
       <c r="J57">
-        <v>1.31E-3</v>
+        <v>1.09E-3</v>
       </c>
       <c r="K57">
-        <v>-20.3125</v>
+        <v>-18.75</v>
       </c>
       <c r="L57">
         <v>1.31E-3</v>
@@ -13311,10 +13308,10 @@
         <v>0</v>
       </c>
       <c r="BG57" s="1">
-        <v>-17.1875</v>
+        <v>-18.75</v>
       </c>
       <c r="BH57" s="1">
-        <v>3.5738899999999999E-6</v>
+        <v>1.0721600000000001E-5</v>
       </c>
       <c r="BI57">
         <v>-18.75</v>
@@ -13347,13 +13344,13 @@
         <v>1.31E-3</v>
       </c>
       <c r="BS57">
-        <v>-20.3125</v>
+        <v>-18.75</v>
       </c>
       <c r="BT57">
         <v>1.31E-3</v>
       </c>
       <c r="BU57">
-        <v>-21.875</v>
+        <v>-18.75</v>
       </c>
       <c r="BV57">
         <v>1.31E-3</v>
@@ -13409,13 +13406,13 @@
         <v>1.31E-3</v>
       </c>
       <c r="I58">
-        <v>-23.4375</v>
+        <v>-20.3125</v>
       </c>
       <c r="J58">
-        <v>1.31E-3</v>
+        <v>1.5200000000000001E-3</v>
       </c>
       <c r="K58">
-        <v>-21.875</v>
+        <v>-20.3125</v>
       </c>
       <c r="L58">
         <v>1.31E-3</v>
@@ -13559,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="BG58">
-        <v>-18.75</v>
+        <v>-20.3125</v>
       </c>
       <c r="BH58" s="1">
-        <v>1.0721600000000001E-5</v>
+        <v>2.5017100000000001E-5</v>
       </c>
       <c r="BI58">
         <v>-20.3125</v>
@@ -13595,13 +13592,13 @@
         <v>1.31E-3</v>
       </c>
       <c r="BS58">
-        <v>-21.875</v>
+        <v>-20.3125</v>
       </c>
       <c r="BT58">
         <v>1.31E-3</v>
       </c>
       <c r="BU58">
-        <v>-23.4375</v>
+        <v>-20.3125</v>
       </c>
       <c r="BV58">
         <v>1.31E-3</v>
@@ -13657,13 +13654,13 @@
         <v>1.31E-3</v>
       </c>
       <c r="I59">
-        <v>-25</v>
+        <v>-21.875</v>
       </c>
       <c r="J59">
-        <v>1.31E-3</v>
+        <v>1.5200000000000001E-3</v>
       </c>
       <c r="K59">
-        <v>-23.4375</v>
+        <v>-21.875</v>
       </c>
       <c r="L59">
         <v>1.31E-3</v>
@@ -13807,10 +13804,10 @@
         <v>0</v>
       </c>
       <c r="BG59">
-        <v>-20.3125</v>
+        <v>-21.875</v>
       </c>
       <c r="BH59" s="1">
-        <v>2.5017100000000001E-5</v>
+        <v>1.07217E-4</v>
       </c>
       <c r="BI59">
         <v>-21.875</v>
@@ -13843,13 +13840,13 @@
         <v>1.31E-3</v>
       </c>
       <c r="BS59">
-        <v>-23.4375</v>
+        <v>-21.875</v>
       </c>
       <c r="BT59">
         <v>1.31E-3</v>
       </c>
       <c r="BU59">
-        <v>-25</v>
+        <v>-21.875</v>
       </c>
       <c r="BV59">
         <v>1.31E-3</v>
@@ -13905,13 +13902,13 @@
         <v>1.31E-3</v>
       </c>
       <c r="I60">
-        <v>-26.5625</v>
+        <v>-23.4375</v>
       </c>
       <c r="J60">
         <v>1.31E-3</v>
       </c>
       <c r="K60">
-        <v>-25</v>
+        <v>-23.4375</v>
       </c>
       <c r="L60">
         <v>1.31E-3</v>
@@ -14055,10 +14052,10 @@
         <v>9.9600000000000001E-3</v>
       </c>
       <c r="BG60">
-        <v>-21.875</v>
+        <v>-23.4375</v>
       </c>
       <c r="BH60" s="1">
-        <v>1.07217E-4</v>
+        <v>-3.2164900000000001E-5</v>
       </c>
       <c r="BI60">
         <v>-23.4375</v>
@@ -14091,13 +14088,13 @@
         <v>1.31E-3</v>
       </c>
       <c r="BS60">
-        <v>-25</v>
+        <v>-23.4375</v>
       </c>
       <c r="BT60">
         <v>1.31E-3</v>
       </c>
       <c r="BU60">
-        <v>-26.5625</v>
+        <v>-23.4375</v>
       </c>
       <c r="BV60">
         <v>1.31E-3</v>
@@ -14153,13 +14150,13 @@
         <v>1.31E-3</v>
       </c>
       <c r="I61">
-        <v>-28.125</v>
+        <v>-25</v>
       </c>
       <c r="J61">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="K61">
-        <v>-26.5625</v>
+        <v>-25</v>
       </c>
       <c r="L61">
         <v>1.31E-3</v>
@@ -14303,10 +14300,10 @@
         <v>1.0670000000000001E-2</v>
       </c>
       <c r="BG61">
-        <v>-23.4375</v>
+        <v>-25</v>
       </c>
       <c r="BH61" s="1">
-        <v>-3.2164900000000001E-5</v>
+        <v>1.102E-2</v>
       </c>
       <c r="BI61">
         <v>-25</v>
@@ -14339,16 +14336,16 @@
         <v>1.31E-3</v>
       </c>
       <c r="BS61">
-        <v>-26.5625</v>
+        <v>-25</v>
       </c>
       <c r="BT61">
         <v>1.31E-3</v>
       </c>
       <c r="BU61">
-        <v>-28.125</v>
+        <v>-25</v>
       </c>
       <c r="BV61">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="BW61">
         <v>-25</v>
@@ -14401,16 +14398,16 @@
         <v>1.31E-3</v>
       </c>
       <c r="I62">
-        <v>-29.6875</v>
+        <v>-26.5625</v>
       </c>
       <c r="J62">
-        <v>1.32E-3</v>
+        <v>1.09E-3</v>
       </c>
       <c r="K62">
-        <v>-28.125</v>
+        <v>-26.5625</v>
       </c>
       <c r="L62">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="M62">
         <v>-26.5625</v>
@@ -14551,10 +14548,10 @@
         <v>1.41E-3</v>
       </c>
       <c r="BG62">
-        <v>-25</v>
+        <v>-26.5625</v>
       </c>
       <c r="BH62">
-        <v>1.102E-2</v>
+        <v>1.18E-2</v>
       </c>
       <c r="BI62">
         <v>-26.5625</v>
@@ -14587,16 +14584,16 @@
         <v>1.31E-3</v>
       </c>
       <c r="BS62">
-        <v>-28.125</v>
+        <v>-26.5625</v>
       </c>
       <c r="BT62">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="BU62">
-        <v>-29.6875</v>
+        <v>-26.5625</v>
       </c>
       <c r="BV62">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="BW62">
         <v>-26.5625</v>
@@ -14649,13 +14646,13 @@
         <v>1.32E-3</v>
       </c>
       <c r="I63">
-        <v>-31.25</v>
+        <v>-28.125</v>
       </c>
       <c r="J63">
-        <v>1.31E-3</v>
+        <v>1.09E-3</v>
       </c>
       <c r="K63">
-        <v>-29.6875</v>
+        <v>-28.125</v>
       </c>
       <c r="L63">
         <v>1.32E-3</v>
@@ -14799,10 +14796,10 @@
         <v>1.58E-3</v>
       </c>
       <c r="BG63">
-        <v>-26.5625</v>
+        <v>-28.125</v>
       </c>
       <c r="BH63">
-        <v>1.18E-2</v>
+        <v>1.31E-3</v>
       </c>
       <c r="BI63">
         <v>-28.125</v>
@@ -14835,16 +14832,16 @@
         <v>1.31E-3</v>
       </c>
       <c r="BS63">
-        <v>-29.6875</v>
+        <v>-28.125</v>
       </c>
       <c r="BT63">
         <v>1.32E-3</v>
       </c>
       <c r="BU63">
-        <v>-31.25</v>
+        <v>-28.125</v>
       </c>
       <c r="BV63">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="BW63">
         <v>-28.125</v>
@@ -14897,16 +14894,16 @@
         <v>1.32E-3</v>
       </c>
       <c r="I64">
-        <v>-32.8125</v>
+        <v>-29.6875</v>
       </c>
       <c r="J64">
         <v>1.31E-3</v>
       </c>
       <c r="K64">
-        <v>-31.25</v>
+        <v>-29.6875</v>
       </c>
       <c r="L64">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="M64">
         <v>-29.6875</v>
@@ -15047,7 +15044,7 @@
         <v>1.74E-3</v>
       </c>
       <c r="BG64">
-        <v>-28.125</v>
+        <v>-29.6875</v>
       </c>
       <c r="BH64">
         <v>1.31E-3</v>
@@ -15083,16 +15080,16 @@
         <v>1.32E-3</v>
       </c>
       <c r="BS64">
-        <v>-31.25</v>
+        <v>-29.6875</v>
       </c>
       <c r="BT64">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="BU64">
-        <v>-32.8125</v>
+        <v>-29.6875</v>
       </c>
       <c r="BV64">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="BW64">
         <v>-29.6875</v>
@@ -15145,13 +15142,13 @@
         <v>1.31E-3</v>
       </c>
       <c r="I65">
-        <v>-34.375</v>
+        <v>-31.25</v>
       </c>
       <c r="J65">
-        <v>1.31E-3</v>
+        <v>1.5200000000000001E-3</v>
       </c>
       <c r="K65">
-        <v>-32.8125</v>
+        <v>-31.25</v>
       </c>
       <c r="L65">
         <v>1.31E-3</v>
@@ -15295,7 +15292,7 @@
         <v>1.5100000000000001E-3</v>
       </c>
       <c r="BG65">
-        <v>-29.6875</v>
+        <v>-31.25</v>
       </c>
       <c r="BH65">
         <v>1.31E-3</v>
@@ -15331,13 +15328,13 @@
         <v>1.31E-3</v>
       </c>
       <c r="BS65">
-        <v>-32.8125</v>
+        <v>-31.25</v>
       </c>
       <c r="BT65">
         <v>1.31E-3</v>
       </c>
       <c r="BU65">
-        <v>-34.375</v>
+        <v>-31.25</v>
       </c>
       <c r="BV65">
         <v>1.31E-3</v>
@@ -15393,13 +15390,13 @@
         <v>1.31E-3</v>
       </c>
       <c r="I66">
-        <v>-35.9375</v>
+        <v>-32.8125</v>
       </c>
       <c r="J66">
         <v>1.31E-3</v>
       </c>
       <c r="K66">
-        <v>-34.375</v>
+        <v>-32.8125</v>
       </c>
       <c r="L66">
         <v>1.31E-3</v>
@@ -15543,7 +15540,7 @@
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="BG66">
-        <v>-31.25</v>
+        <v>-32.8125</v>
       </c>
       <c r="BH66">
         <v>1.31E-3</v>
@@ -15579,13 +15576,13 @@
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="BS66">
-        <v>-34.375</v>
+        <v>-32.8125</v>
       </c>
       <c r="BT66">
         <v>1.31E-3</v>
       </c>
       <c r="BU66">
-        <v>-35.9375</v>
+        <v>-32.8125</v>
       </c>
       <c r="BV66">
         <v>1.31E-3</v>
@@ -15641,13 +15638,13 @@
         <v>1.31E-3</v>
       </c>
       <c r="I67">
-        <v>-37.5</v>
+        <v>-34.375</v>
       </c>
       <c r="J67">
-        <v>1.32E-3</v>
+        <v>1.1100000000000001E-3</v>
       </c>
       <c r="K67">
-        <v>-35.9375</v>
+        <v>-34.375</v>
       </c>
       <c r="L67">
         <v>1.31E-3</v>
@@ -15791,7 +15788,7 @@
         <v>1.31E-3</v>
       </c>
       <c r="BG67">
-        <v>-32.8125</v>
+        <v>-34.375</v>
       </c>
       <c r="BH67">
         <v>1.31E-3</v>
@@ -15827,16 +15824,16 @@
         <v>1.31E-3</v>
       </c>
       <c r="BS67">
-        <v>-35.9375</v>
+        <v>-34.375</v>
       </c>
       <c r="BT67">
         <v>1.31E-3</v>
       </c>
       <c r="BU67">
-        <v>-37.5</v>
+        <v>-34.375</v>
       </c>
       <c r="BV67">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="BW67">
         <v>-34.375</v>
@@ -15889,16 +15886,16 @@
         <v>1.31E-3</v>
       </c>
       <c r="I68">
-        <v>-39.0625</v>
+        <v>-35.9375</v>
       </c>
       <c r="J68">
-        <v>1.32E-3</v>
+        <v>1.2700000000000001E-3</v>
       </c>
       <c r="K68">
-        <v>-37.5</v>
+        <v>-35.9375</v>
       </c>
       <c r="L68">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="M68">
         <v>-35.9375</v>
@@ -16039,7 +16036,7 @@
         <v>1.31E-3</v>
       </c>
       <c r="BG68">
-        <v>-34.375</v>
+        <v>-35.9375</v>
       </c>
       <c r="BH68">
         <v>1.31E-3</v>
@@ -16075,16 +16072,16 @@
         <v>1.31E-3</v>
       </c>
       <c r="BS68">
-        <v>-37.5</v>
+        <v>-35.9375</v>
       </c>
       <c r="BT68">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="BU68">
-        <v>-39.0625</v>
+        <v>-35.9375</v>
       </c>
       <c r="BV68">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="BW68">
         <v>-35.9375</v>
@@ -16137,13 +16134,13 @@
         <v>1.32E-3</v>
       </c>
       <c r="I69">
-        <v>-40.625</v>
+        <v>-37.5</v>
       </c>
       <c r="J69">
-        <v>1.31E-3</v>
+        <v>1.3500000000000001E-3</v>
       </c>
       <c r="K69">
-        <v>-39.0625</v>
+        <v>-37.5</v>
       </c>
       <c r="L69">
         <v>1.32E-3</v>
@@ -16287,7 +16284,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="BG69">
-        <v>-35.9375</v>
+        <v>-37.5</v>
       </c>
       <c r="BH69">
         <v>1.31E-3</v>
@@ -16323,16 +16320,16 @@
         <v>1.31E-3</v>
       </c>
       <c r="BS69">
-        <v>-39.0625</v>
+        <v>-37.5</v>
       </c>
       <c r="BT69">
         <v>1.32E-3</v>
       </c>
       <c r="BU69">
-        <v>-40.625</v>
+        <v>-37.5</v>
       </c>
       <c r="BV69">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="BW69">
         <v>-37.5</v>
@@ -16385,16 +16382,16 @@
         <v>1.32E-3</v>
       </c>
       <c r="I70">
-        <v>-42.1875</v>
+        <v>-39.0625</v>
       </c>
       <c r="J70">
-        <v>1.31E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="K70">
-        <v>-40.625</v>
+        <v>-39.0625</v>
       </c>
       <c r="L70">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="M70">
         <v>-39.0625</v>
@@ -16535,10 +16532,10 @@
         <v>1.32E-3</v>
       </c>
       <c r="BG70">
-        <v>-37.5</v>
+        <v>-39.0625</v>
       </c>
       <c r="BH70">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="BI70">
         <v>-39.0625</v>
@@ -16571,16 +16568,16 @@
         <v>1.32E-3</v>
       </c>
       <c r="BS70">
-        <v>-40.625</v>
+        <v>-39.0625</v>
       </c>
       <c r="BT70">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="BU70">
-        <v>-42.1875</v>
+        <v>-39.0625</v>
       </c>
       <c r="BV70">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="BW70">
         <v>-39.0625</v>
@@ -16633,13 +16630,13 @@
         <v>1.31E-3</v>
       </c>
       <c r="I71">
-        <v>-43.75</v>
+        <v>-40.625</v>
       </c>
       <c r="J71">
         <v>1.31E-3</v>
       </c>
       <c r="K71">
-        <v>-42.1875</v>
+        <v>-40.625</v>
       </c>
       <c r="L71">
         <v>1.31E-3</v>
@@ -16783,10 +16780,10 @@
         <v>1.31E-3</v>
       </c>
       <c r="BG71">
-        <v>-39.0625</v>
+        <v>-40.625</v>
       </c>
       <c r="BH71">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="BI71">
         <v>-40.625</v>
@@ -16819,13 +16816,13 @@
         <v>1.31E-3</v>
       </c>
       <c r="BS71">
-        <v>-42.1875</v>
+        <v>-40.625</v>
       </c>
       <c r="BT71">
         <v>1.31E-3</v>
       </c>
       <c r="BU71">
-        <v>-43.75</v>
+        <v>-40.625</v>
       </c>
       <c r="BV71">
         <v>1.31E-3</v>
@@ -16881,13 +16878,13 @@
         <v>1.31E-3</v>
       </c>
       <c r="I72">
-        <v>-45.3125</v>
+        <v>-42.1875</v>
       </c>
       <c r="J72">
         <v>1.31E-3</v>
       </c>
       <c r="K72">
-        <v>-43.75</v>
+        <v>-42.1875</v>
       </c>
       <c r="L72">
         <v>1.31E-3</v>
@@ -17031,7 +17028,7 @@
         <v>1.31E-3</v>
       </c>
       <c r="BG72">
-        <v>-40.625</v>
+        <v>-42.1875</v>
       </c>
       <c r="BH72">
         <v>1.31E-3</v>
@@ -17067,13 +17064,13 @@
         <v>1.31E-3</v>
       </c>
       <c r="BS72">
-        <v>-43.75</v>
+        <v>-42.1875</v>
       </c>
       <c r="BT72">
         <v>1.31E-3</v>
       </c>
       <c r="BU72">
-        <v>-45.3125</v>
+        <v>-42.1875</v>
       </c>
       <c r="BV72">
         <v>1.31E-3</v>
@@ -17129,13 +17126,13 @@
         <v>1.31E-3</v>
       </c>
       <c r="I73">
-        <v>-46.875</v>
+        <v>-43.75</v>
       </c>
       <c r="J73">
         <v>1.31E-3</v>
       </c>
       <c r="K73">
-        <v>-45.3125</v>
+        <v>-43.75</v>
       </c>
       <c r="L73">
         <v>1.31E-3</v>
@@ -17279,7 +17276,7 @@
         <v>1.31E-3</v>
       </c>
       <c r="BG73">
-        <v>-42.1875</v>
+        <v>-43.75</v>
       </c>
       <c r="BH73">
         <v>1.31E-3</v>
@@ -17315,13 +17312,13 @@
         <v>1.31E-3</v>
       </c>
       <c r="BS73">
-        <v>-45.3125</v>
+        <v>-43.75</v>
       </c>
       <c r="BT73">
         <v>1.31E-3</v>
       </c>
       <c r="BU73">
-        <v>-46.875</v>
+        <v>-43.75</v>
       </c>
       <c r="BV73">
         <v>1.31E-3</v>
@@ -17377,13 +17374,13 @@
         <v>1.31E-3</v>
       </c>
       <c r="I74">
-        <v>-48.4375</v>
+        <v>-45.3125</v>
       </c>
       <c r="J74">
         <v>1.31E-3</v>
       </c>
       <c r="K74">
-        <v>-46.875</v>
+        <v>-45.3125</v>
       </c>
       <c r="L74">
         <v>1.31E-3</v>
@@ -17527,7 +17524,7 @@
         <v>1.31E-3</v>
       </c>
       <c r="BG74">
-        <v>-43.75</v>
+        <v>-45.3125</v>
       </c>
       <c r="BH74">
         <v>1.31E-3</v>
@@ -17563,13 +17560,13 @@
         <v>1.31E-3</v>
       </c>
       <c r="BS74">
-        <v>-46.875</v>
+        <v>-45.3125</v>
       </c>
       <c r="BT74">
         <v>1.31E-3</v>
       </c>
       <c r="BU74">
-        <v>-48.4375</v>
+        <v>-45.3125</v>
       </c>
       <c r="BV74">
         <v>1.31E-3</v>
@@ -17625,13 +17622,13 @@
         <v>1.31E-3</v>
       </c>
       <c r="I75">
-        <v>-50</v>
+        <v>-46.875</v>
       </c>
       <c r="J75">
-        <v>1.33E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="K75">
-        <v>-48.4375</v>
+        <v>-46.875</v>
       </c>
       <c r="L75">
         <v>1.31E-3</v>
@@ -17775,7 +17772,7 @@
         <v>1.31E-3</v>
       </c>
       <c r="BG75">
-        <v>-45.3125</v>
+        <v>-46.875</v>
       </c>
       <c r="BH75">
         <v>1.31E-3</v>
@@ -17811,16 +17808,16 @@
         <v>1.32E-3</v>
       </c>
       <c r="BS75">
-        <v>-48.4375</v>
+        <v>-46.875</v>
       </c>
       <c r="BT75">
         <v>1.31E-3</v>
       </c>
       <c r="BU75">
-        <v>-50</v>
+        <v>-46.875</v>
       </c>
       <c r="BV75">
-        <v>1.33E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="BW75">
         <v>-46.875</v>
@@ -17873,16 +17870,16 @@
         <v>1.31E-3</v>
       </c>
       <c r="I76">
-        <v>-51.5625</v>
+        <v>-48.4375</v>
       </c>
       <c r="J76">
-        <v>1.33E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="K76">
-        <v>-50</v>
+        <v>-48.4375</v>
       </c>
       <c r="L76">
-        <v>1.33E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="M76">
         <v>-48.4375</v>
@@ -18023,7 +18020,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="BG76">
-        <v>-46.875</v>
+        <v>-48.4375</v>
       </c>
       <c r="BH76">
         <v>1.31E-3</v>
@@ -18059,16 +18056,16 @@
         <v>1.32E-3</v>
       </c>
       <c r="BS76">
-        <v>-50</v>
+        <v>-48.4375</v>
       </c>
       <c r="BT76">
-        <v>1.33E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="BU76">
-        <v>-51.5625</v>
+        <v>-48.4375</v>
       </c>
       <c r="BV76">
-        <v>1.33E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="BW76">
         <v>-48.4375</v>
@@ -18121,13 +18118,13 @@
         <v>1.33E-3</v>
       </c>
       <c r="I77">
-        <v>-53.125</v>
+        <v>-50</v>
       </c>
       <c r="J77">
-        <v>1.32E-3</v>
+        <v>1.33E-3</v>
       </c>
       <c r="K77">
-        <v>-51.5625</v>
+        <v>-50</v>
       </c>
       <c r="L77">
         <v>1.33E-3</v>
@@ -18271,10 +18268,10 @@
         <v>1.33E-3</v>
       </c>
       <c r="BG77">
-        <v>-48.4375</v>
+        <v>-50</v>
       </c>
       <c r="BH77">
-        <v>1.31E-3</v>
+        <v>1.33E-3</v>
       </c>
       <c r="BI77">
         <v>-50</v>
@@ -18307,16 +18304,16 @@
         <v>1.33E-3</v>
       </c>
       <c r="BS77">
-        <v>-51.5625</v>
+        <v>-50</v>
       </c>
       <c r="BT77">
         <v>1.33E-3</v>
       </c>
       <c r="BU77">
-        <v>-53.125</v>
+        <v>-50</v>
       </c>
       <c r="BV77">
-        <v>1.32E-3</v>
+        <v>1.33E-3</v>
       </c>
       <c r="BW77">
         <v>-50</v>
@@ -18369,16 +18366,16 @@
         <v>1.33E-3</v>
       </c>
       <c r="I78">
-        <v>-54.6875</v>
+        <v>-51.5625</v>
       </c>
       <c r="J78">
-        <v>1.32E-3</v>
+        <v>1.33E-3</v>
       </c>
       <c r="K78">
-        <v>-53.125</v>
+        <v>-51.5625</v>
       </c>
       <c r="L78">
-        <v>1.32E-3</v>
+        <v>1.33E-3</v>
       </c>
       <c r="M78">
         <v>-51.5625</v>
@@ -18519,7 +18516,7 @@
         <v>1.33E-3</v>
       </c>
       <c r="BG78">
-        <v>-50</v>
+        <v>-51.5625</v>
       </c>
       <c r="BH78">
         <v>1.33E-3</v>
@@ -18555,16 +18552,16 @@
         <v>1.33E-3</v>
       </c>
       <c r="BS78">
-        <v>-53.125</v>
+        <v>-51.5625</v>
       </c>
       <c r="BT78">
-        <v>1.32E-3</v>
+        <v>1.33E-3</v>
       </c>
       <c r="BU78">
-        <v>-54.6875</v>
+        <v>-51.5625</v>
       </c>
       <c r="BV78">
-        <v>1.32E-3</v>
+        <v>1.33E-3</v>
       </c>
       <c r="BW78">
         <v>-51.5625</v>
@@ -18617,13 +18614,13 @@
         <v>1.32E-3</v>
       </c>
       <c r="I79">
-        <v>-56.25</v>
+        <v>-53.125</v>
       </c>
       <c r="J79">
         <v>1.31E-3</v>
       </c>
       <c r="K79">
-        <v>-54.6875</v>
+        <v>-53.125</v>
       </c>
       <c r="L79">
         <v>1.32E-3</v>
@@ -18767,10 +18764,10 @@
         <v>1.31E-3</v>
       </c>
       <c r="BG79">
-        <v>-51.5625</v>
+        <v>-53.125</v>
       </c>
       <c r="BH79">
-        <v>1.33E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="BI79">
         <v>-53.125</v>
@@ -18803,16 +18800,16 @@
         <v>1.31E-3</v>
       </c>
       <c r="BS79">
-        <v>-54.6875</v>
+        <v>-53.125</v>
       </c>
       <c r="BT79">
         <v>1.32E-3</v>
       </c>
       <c r="BU79">
-        <v>-56.25</v>
+        <v>-53.125</v>
       </c>
       <c r="BV79">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="BW79">
         <v>-53.125</v>
@@ -18865,16 +18862,16 @@
         <v>1.32E-3</v>
       </c>
       <c r="I80">
-        <v>-57.8125</v>
+        <v>-54.6875</v>
       </c>
       <c r="J80">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="K80">
-        <v>-56.25</v>
+        <v>-54.6875</v>
       </c>
       <c r="L80">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="M80">
         <v>-54.6875</v>
@@ -19015,10 +19012,10 @@
         <v>1.32E-3</v>
       </c>
       <c r="BG80">
-        <v>-53.125</v>
+        <v>-54.6875</v>
       </c>
       <c r="BH80">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="BI80">
         <v>-54.6875</v>
@@ -19051,13 +19048,13 @@
         <v>1.32E-3</v>
       </c>
       <c r="BS80">
-        <v>-56.25</v>
+        <v>-54.6875</v>
       </c>
       <c r="BT80">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="BU80">
-        <v>-57.8125</v>
+        <v>-54.6875</v>
       </c>
       <c r="BV80">
         <v>1.32E-3</v>
@@ -19113,16 +19110,16 @@
         <v>1.31E-3</v>
       </c>
       <c r="I81">
-        <v>-59.375</v>
+        <v>-56.25</v>
       </c>
       <c r="J81">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="K81">
-        <v>-57.8125</v>
+        <v>-56.25</v>
       </c>
       <c r="L81">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="M81">
         <v>-56.25</v>
@@ -19263,10 +19260,10 @@
         <v>1.31E-3</v>
       </c>
       <c r="BG81">
-        <v>-54.6875</v>
+        <v>-56.25</v>
       </c>
       <c r="BH81">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="BI81">
         <v>-56.25</v>
@@ -19299,16 +19296,16 @@
         <v>1.31E-3</v>
       </c>
       <c r="BS81">
-        <v>-57.8125</v>
+        <v>-56.25</v>
       </c>
       <c r="BT81">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="BU81">
-        <v>-59.375</v>
+        <v>-56.25</v>
       </c>
       <c r="BV81">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="BW81">
         <v>-56.25</v>
@@ -19361,13 +19358,13 @@
         <v>1.32E-3</v>
       </c>
       <c r="I82">
-        <v>-60.9375</v>
+        <v>-57.8125</v>
       </c>
       <c r="J82">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="K82">
-        <v>-59.375</v>
+        <v>-57.8125</v>
       </c>
       <c r="L82">
         <v>1.32E-3</v>
@@ -19511,10 +19508,10 @@
         <v>1.31E-3</v>
       </c>
       <c r="BG82">
-        <v>-56.25</v>
+        <v>-57.8125</v>
       </c>
       <c r="BH82">
-        <v>1.31E-3</v>
+        <v>1.32E-3</v>
       </c>
       <c r="BI82">
         <v>-57.8125</v>
@@ -19547,13 +19544,13 @@
         <v>1.32E-3</v>
       </c>
       <c r="BS82">
-        <v>-59.375</v>
+        <v>-57.8125</v>
       </c>
       <c r="BT82">
         <v>1.32E-3</v>
       </c>
       <c r="BU82">
-        <v>-60.9375</v>
+        <v>-57.8125</v>
       </c>
       <c r="BV82">
         <v>1.32E-3</v>
@@ -19608,8 +19605,14 @@
       <c r="H83">
         <v>1.32E-3</v>
       </c>
+      <c r="I83">
+        <v>-59.375</v>
+      </c>
+      <c r="J83">
+        <v>1.32E-3</v>
+      </c>
       <c r="K83">
-        <v>-60.9375</v>
+        <v>-59.375</v>
       </c>
       <c r="L83">
         <v>1.32E-3</v>
@@ -19753,7 +19756,7 @@
         <v>1.32E-3</v>
       </c>
       <c r="BG83">
-        <v>-57.8125</v>
+        <v>-59.375</v>
       </c>
       <c r="BH83">
         <v>1.32E-3</v>
@@ -19789,9 +19792,15 @@
         <v>1.32E-3</v>
       </c>
       <c r="BS83">
-        <v>-60.9375</v>
+        <v>-59.375</v>
       </c>
       <c r="BT83">
+        <v>1.32E-3</v>
+      </c>
+      <c r="BU83">
+        <v>-59.375</v>
+      </c>
+      <c r="BV83">
         <v>1.32E-3</v>
       </c>
       <c r="BW83">
@@ -19844,6 +19853,18 @@
       <c r="H84">
         <v>1.32E-3</v>
       </c>
+      <c r="I84">
+        <v>-60.9375</v>
+      </c>
+      <c r="J84">
+        <v>1.32E-3</v>
+      </c>
+      <c r="K84">
+        <v>-60.9375</v>
+      </c>
+      <c r="L84">
+        <v>1.32E-3</v>
+      </c>
       <c r="M84">
         <v>-60.9375</v>
       </c>
@@ -19983,10 +20004,10 @@
         <v>1.32E-3</v>
       </c>
       <c r="BG84">
-        <v>-59.375</v>
+        <v>-60.9375</v>
       </c>
       <c r="BH84">
-        <v>1.32E-3</v>
+        <v>1.31E-3</v>
       </c>
       <c r="BI84">
         <v>-60.9375</v>
@@ -20016,6 +20037,18 @@
         <v>-60.9375</v>
       </c>
       <c r="BR84">
+        <v>1.32E-3</v>
+      </c>
+      <c r="BS84">
+        <v>-60.9375</v>
+      </c>
+      <c r="BT84">
+        <v>1.32E-3</v>
+      </c>
+      <c r="BU84">
+        <v>-60.9375</v>
+      </c>
+      <c r="BV84">
         <v>1.32E-3</v>
       </c>
       <c r="BW84">
